--- a/capabilities/marginal-analysis/model.xlsx
+++ b/capabilities/marginal-analysis/model.xlsx
@@ -43,8 +43,7 @@
     <definedName name="BEDS_TOMATO">'Optimization'!$B$5</definedName>
     <definedName name="BEDS_CARROT">'Optimization'!$B$6</definedName>
     <definedName name="BEDS_MESCLUN">'Optimization'!$B$7</definedName>
-    <definedName name="SEASON_PROFIT_OBJ">'Optimization'!$B$10</definedName>
-    <definedName name="CONSTRAINTS_ALL">'Optimization'!$D$19</definedName>
+    <definedName name="CONSTRAINTS_ALL">'Optimization'!$D$25</definedName>
     <definedName name="TOTAL_LABOR_HRS">'Cost structure'!$B$8</definedName>
     <definedName name="FARMER_HRS_USED">'Cost structure'!$B$11</definedName>
     <definedName name="TEMP_HRS_USED">'Cost structure'!$B$12</definedName>
@@ -61,6 +60,42 @@
     <definedName name="PMC_TOM">'MC schedules'!$F$29</definedName>
     <definedName name="PMC_CAR">'MC schedules'!$P$29</definedName>
     <definedName name="PMC_MES">'MC schedules'!$Z$39</definedName>
+    <definedName name="solver_opt" localSheetId="1" hidden="1">Optimization!$B$16</definedName>
+    <definedName name="solver_typ" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_val" localSheetId="1" hidden="1">0</definedName>
+    <definedName name="solver_adj" localSheetId="1" hidden="1">Optimization!$B$5:$B$7</definedName>
+    <definedName name="solver_eng" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_num" localSheetId="1" hidden="1">4</definedName>
+    <definedName name="solver_lhs1" localSheetId="1" hidden="1">Optimization!$B$5:$B$7</definedName>
+    <definedName name="solver_rel1" localSheetId="1" hidden="1">4</definedName>
+    <definedName name="solver_rhs1" localSheetId="1" hidden="1">integer</definedName>
+    <definedName name="solver_lhs2" localSheetId="1" hidden="1">Optimization!$B$5:$B$7</definedName>
+    <definedName name="solver_rel2" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_rhs2" localSheetId="1" hidden="1">Optimization!$C$5:$C$7</definedName>
+    <definedName name="solver_lhs3" localSheetId="1" hidden="1">Optimization!$B$10</definedName>
+    <definedName name="solver_rel3" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_rhs3" localSheetId="1" hidden="1">Optimization!$C$10</definedName>
+    <definedName name="solver_lhs4" localSheetId="1" hidden="1">Optimization!$B$11</definedName>
+    <definedName name="solver_rel4" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_rhs4" localSheetId="1" hidden="1">Optimization!$C$11</definedName>
+    <definedName name="solver_pre" localSheetId="1" hidden="1">0.000001</definedName>
+    <definedName name="solver_tol" localSheetId="1" hidden="1">0.01</definedName>
+    <definedName name="solver_itr" localSheetId="1" hidden="1">2147483647</definedName>
+    <definedName name="solver_ver" localSheetId="1" hidden="1">3</definedName>
+    <definedName name="solver_drv" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_sho" localSheetId="1" hidden="1">2</definedName>
+    <definedName name="solver_scl" localSheetId="1" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="1" hidden="1">2</definedName>
+    <definedName name="solver_ssz" localSheetId="1" hidden="1">2</definedName>
+    <definedName name="solver_mni" localSheetId="1" hidden="1">30</definedName>
+    <definedName name="solver_mrt" localSheetId="1" hidden="1">0.075</definedName>
+    <definedName name="solver_nod" localSheetId="1" hidden="1">2147483647</definedName>
+    <definedName name="solver_rsd" localSheetId="1" hidden="1">0</definedName>
+    <definedName name="solver_pop" localSheetId="1" hidden="1">100</definedName>
+    <definedName name="solver_rbv" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_time" localSheetId="1" hidden="1">2147483647</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -113,7 +148,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -128,6 +163,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -157,7 +197,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -173,20 +213,21 @@
     <xf numFmtId="167" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -1041,13 +1082,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="54" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1060,16 +1102,28 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Solver changing cells are B5:B7. Set them to 0/0/0 or 20/0/0 before each Solver run.</t>
+          <t>The Solver model is already saved in this workbook. Open Data &gt; Solver and it loads configured — just press Solve.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Decision variables</t>
-        </is>
-      </c>
+          <t>Decision variables — Solver changing cells</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Beds (change these)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Cap</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
@@ -1080,9 +1134,13 @@
       <c r="B5" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Integer, at least 0, at most MAX_BEDS_TOM</t>
+      <c r="C5" s="15">
+        <f>MAX_BEDS_TOM</f>
+        <v/>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Integer, at least 0, at most the cap</t>
         </is>
       </c>
     </row>
@@ -1095,9 +1153,13 @@
       <c r="B6" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Integer, at least 0, at most MAX_BEDS_CAR</t>
+      <c r="C6" s="15">
+        <f>MAX_BEDS_CAR</f>
+        <v/>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Integer, at least 0, at most the cap</t>
         </is>
       </c>
     </row>
@@ -1110,303 +1172,292 @@
       <c r="B7" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Integer, at least 0, at most MAX_BEDS_MES</t>
+      <c r="C7" s="15">
+        <f>MAX_BEDS_MES</f>
+        <v/>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Integer, at least 0, at most the cap</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Objective</t>
+          <t>Constraint quantities — Solver constrains these</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>Season profit  (maximize)</t>
-        </is>
-      </c>
-      <c r="B10" s="15">
+          <t>Total beds planted</t>
+        </is>
+      </c>
+      <c r="B10" s="16">
+        <f>SUM(B5:B7)</f>
+        <v/>
+      </c>
+      <c r="C10" s="15">
+        <f>TOTAL_BED_CAP</f>
+        <v/>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>At most 64</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Temporary hours needed</t>
+        </is>
+      </c>
+      <c r="B11" s="17">
+        <f>TEMP_HRS_USED</f>
+        <v/>
+      </c>
+      <c r="C11" s="17">
+        <f>MAX_TEMPS*TEMP_HRS_EACH</f>
+        <v/>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>At most 4 workers x 1,440 hours = 5,760. Equivalent to "at most 4 workers", but smooth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>ROUNDUP is deliberately kept OUT of the Solver constraint: GRG Nonlinear assumes smooth</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>Temporary workers required (reported)</t>
+        </is>
+      </c>
+      <c r="B13" s="15">
+        <f>TEMPS_REQUIRED</f>
+        <v/>
+      </c>
+      <c r="C13" s="15">
+        <f>MAX_TEMPS</f>
+        <v/>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>functions, and a step function here makes it stall. The headcount is still reported below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Objective — Solver maximizes this cell</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Season profit</t>
+        </is>
+      </c>
+      <c r="B16" s="18">
         <f>SEASON_PROFIT</f>
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Constraint checks</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Constraint</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Limit</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Tomato beds at most MAX_BEDS</t>
-        </is>
-      </c>
-      <c r="B14" s="16">
-        <f>BEDS_TOMATO</f>
-        <v/>
-      </c>
-      <c r="C14" s="16">
-        <f>MAX_BEDS_TOM</f>
-        <v/>
-      </c>
-      <c r="D14" s="17">
-        <f>IF(B14&lt;=C14,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Carrot beds at most MAX_BEDS</t>
-        </is>
-      </c>
-      <c r="B15" s="16">
-        <f>BEDS_CARROT</f>
-        <v/>
-      </c>
-      <c r="C15" s="16">
-        <f>MAX_BEDS_CAR</f>
-        <v/>
-      </c>
-      <c r="D15" s="17">
-        <f>IF(B15&lt;=C15,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Mesclun beds at most MAX_BEDS</t>
-        </is>
-      </c>
-      <c r="B16" s="16">
-        <f>BEDS_MESCLUN</f>
-        <v/>
-      </c>
-      <c r="C16" s="16">
-        <f>MAX_BEDS_MES</f>
-        <v/>
-      </c>
-      <c r="D16" s="17">
-        <f>IF(B16&lt;=C16,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Total beds at most TOTAL_BED_CAP</t>
-        </is>
-      </c>
-      <c r="B17" s="16">
-        <f>BEDS_TOMATO+BEDS_CARROT+BEDS_MESCLUN</f>
-        <v/>
-      </c>
-      <c r="C17" s="16">
-        <f>TOTAL_BED_CAP</f>
-        <v/>
-      </c>
-      <c r="D17" s="17">
-        <f>IF(B17&lt;=C17,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Temp workers at most MAX_TEMPS</t>
-        </is>
-      </c>
-      <c r="B18" s="16">
-        <f>TEMPS_REQUIRED</f>
-        <v/>
-      </c>
-      <c r="C18" s="16">
-        <f>MAX_TEMPS</f>
-        <v/>
-      </c>
-      <c r="D18" s="17">
-        <f>IF(B18&lt;=C18,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Tomato beds at most cap</t>
+        </is>
+      </c>
+      <c r="B20" s="16">
+        <f>B5</f>
+        <v/>
+      </c>
+      <c r="C20" s="16">
+        <f>C5</f>
+        <v/>
+      </c>
+      <c r="D20" s="19">
+        <f>IF(B20&lt;=C20,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Carrot beds at most cap</t>
+        </is>
+      </c>
+      <c r="B21" s="16">
+        <f>B6</f>
+        <v/>
+      </c>
+      <c r="C21" s="16">
+        <f>C6</f>
+        <v/>
+      </c>
+      <c r="D21" s="19">
+        <f>IF(B21&lt;=C21,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Mesclun beds at most cap</t>
+        </is>
+      </c>
+      <c r="B22" s="16">
+        <f>B7</f>
+        <v/>
+      </c>
+      <c r="C22" s="16">
+        <f>C7</f>
+        <v/>
+      </c>
+      <c r="D22" s="19">
+        <f>IF(B22&lt;=C22,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Total beds at most 64</t>
+        </is>
+      </c>
+      <c r="B23" s="16">
+        <f>B10</f>
+        <v/>
+      </c>
+      <c r="C23" s="16">
+        <f>C10</f>
+        <v/>
+      </c>
+      <c r="D23" s="19">
+        <f>IF(B23&lt;=C23,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Temp workers at most 4</t>
+        </is>
+      </c>
+      <c r="B24" s="16">
+        <f>B13</f>
+        <v/>
+      </c>
+      <c r="C24" s="16">
+        <f>C13</f>
+        <v/>
+      </c>
+      <c r="D24" s="19">
+        <f>IF(B24&lt;=C24,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>All constraints</t>
         </is>
       </c>
-      <c r="D19" s="17">
-        <f>IF(COUNTIF(D14:D18,"PASS")=5,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Solver settings — enter these in Excel (Data &gt; Solver)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t>Set Objective</t>
-        </is>
-      </c>
-      <c r="B22" s="13" t="inlineStr">
-        <is>
-          <t>$B$10</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="13" t="inlineStr">
-        <is>
-          <t>To</t>
-        </is>
-      </c>
-      <c r="B23" s="13" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>By Changing Variable Cells</t>
-        </is>
-      </c>
-      <c r="B24" s="13" t="inlineStr">
-        <is>
-          <t>$B$5:$B$7</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="13" t="inlineStr">
-        <is>
-          <t>Subject to the Constraints</t>
-        </is>
-      </c>
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>$B$5:$B$7 = integer</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="13" t="inlineStr"/>
-      <c r="B26" s="13" t="inlineStr">
-        <is>
-          <t>$B$5:$B$7 &gt;= 0</t>
-        </is>
+      <c r="D25" s="19">
+        <f>IF(COUNTIF(D20:D24,"PASS")=5,"PASS","FAIL")</f>
+        <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr"/>
-      <c r="B27" s="13" t="inlineStr">
-        <is>
-          <t>$B$14 &lt;= $C$14      (tomato cap)</t>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>How to run the audit</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="inlineStr"/>
-      <c r="B28" s="13" t="inlineStr">
-        <is>
-          <t>$B$15 &lt;= $C$15      (carrot cap)</t>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>1. Set B5:B7 to 0, 0, 0.  Data &gt; Solver &gt; Solve.  Record the answer on the Checks sheet.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="13" t="inlineStr"/>
-      <c r="B29" s="13" t="inlineStr">
-        <is>
-          <t>$B$16 &lt;= $C$16      (mesclun cap)</t>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2. Set B5:B7 to 20, 0, 0.  Data &gt; Solver &gt; Solve again.  Record that answer too.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="13" t="inlineStr"/>
-      <c r="B30" s="13" t="inlineStr">
-        <is>
-          <t>$B$17 &lt;= $C$17      (64 beds total)</t>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>3. If the two runs disagree, that is a finding — GRG Nonlinear stops at the first summit it reaches.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="inlineStr"/>
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>$B$18 &lt;= $C$18      (4 temp workers)</t>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>4. Read the Checks sheet: twelve rules, each PASS or FAIL.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="13" t="inlineStr">
-        <is>
-          <t>Solving Method</t>
-        </is>
-      </c>
-      <c r="B32" s="13" t="inlineStr">
-        <is>
-          <t>GRG Nonlinear</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="13" t="inlineStr">
-        <is>
-          <t>Make Unconstrained Variables Non-Negative</t>
-        </is>
-      </c>
-      <c r="B33" s="13" t="inlineStr">
-        <is>
-          <t>checked</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Audit: run Solver from B5:B7 = 0/0/0, record the answer, then reset to 20/0/0 and run again.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>GRG Nonlinear stops at the first summit it reaches, so the two runs are a real test, not a formality.</t>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>If Solver is missing from the Data ribbon: File &gt; Options &gt; Add-ins &gt; Manage: Excel Add-ins &gt; Go &gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>tick Solver Add-in.  On Mac: Tools &gt; Excel Add-ins &gt; tick Solver.</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1509,7 @@
           <t>Tomato labor hours</t>
         </is>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="17">
         <f>BEDS_TOMATO*HRS_PER_BED_WEEK_TOM*WEEKS*(1+DIM_PCT_TOM)^BEDS_TOMATO</f>
         <v/>
       </c>
@@ -1474,7 +1525,7 @@
           <t>Carrot labor hours</t>
         </is>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="17">
         <f>BEDS_CARROT*HRS_PER_BED_WEEK_CAR*WEEKS*(1+DIM_PCT_CAR)^BEDS_CARROT</f>
         <v/>
       </c>
@@ -1485,7 +1536,7 @@
           <t>Mesclun labor hours</t>
         </is>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="17">
         <f>BEDS_MESCLUN*HRS_PER_BED_WEEK_MES*WEEKS*(1+DIM_PCT_MES)^BEDS_MESCLUN</f>
         <v/>
       </c>
@@ -1574,7 +1625,7 @@
           <t>FARMER_LABOR_COST</t>
         </is>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="20">
         <f>FARMER_HRS_USED*FARMER_RATE</f>
         <v/>
       </c>
@@ -1590,7 +1641,7 @@
           <t>TEMP_LABOR_COST</t>
         </is>
       </c>
-      <c r="B17" s="19">
+      <c r="B17" s="20">
         <f>TEMP_HRS_USED*TEMP_RATE</f>
         <v/>
       </c>
@@ -1606,7 +1657,7 @@
           <t>TOTAL_LABOR_COST</t>
         </is>
       </c>
-      <c r="B18" s="19">
+      <c r="B18" s="20">
         <f>FARMER_LABOR_COST+TEMP_LABOR_COST</f>
         <v/>
       </c>
@@ -1647,7 +1698,7 @@
           <t>Tomato labor cost</t>
         </is>
       </c>
-      <c r="B23" s="19">
+      <c r="B23" s="20">
         <f>B5*BLENDED_RATE</f>
         <v/>
       </c>
@@ -1658,7 +1709,7 @@
           <t>Carrot labor cost</t>
         </is>
       </c>
-      <c r="B24" s="19">
+      <c r="B24" s="20">
         <f>B6*BLENDED_RATE</f>
         <v/>
       </c>
@@ -1669,7 +1720,7 @@
           <t>Mesclun labor cost</t>
         </is>
       </c>
-      <c r="B25" s="19">
+      <c r="B25" s="20">
         <f>B7*BLENDED_RATE</f>
         <v/>
       </c>
@@ -1680,7 +1731,7 @@
           <t>Check: allocation equals total</t>
         </is>
       </c>
-      <c r="B26" s="19">
+      <c r="B26" s="20">
         <f>SUM(B23:B25)</f>
         <v/>
       </c>
@@ -1703,7 +1754,7 @@
           <t>SEASON_REVENUE</t>
         </is>
       </c>
-      <c r="B29" s="15">
+      <c r="B29" s="21">
         <f>BEDS_TOMATO*PRICE_PER_BED_TOM+BEDS_CARROT*PRICE_PER_BED_CAR+BEDS_MESCLUN*PRICE_PER_BED_MES</f>
         <v/>
       </c>
@@ -1719,7 +1770,7 @@
           <t>FERTILIZER_COST</t>
         </is>
       </c>
-      <c r="B30" s="15">
+      <c r="B30" s="21">
         <f>BEDS_TOMATO*FERTILIZER_PER_BED_TOM+BEDS_CARROT*FERTILIZER_PER_BED_CAR+BEDS_MESCLUN*FERTILIZER_PER_BED_MES</f>
         <v/>
       </c>
@@ -1735,7 +1786,7 @@
           <t>Fixed costs</t>
         </is>
       </c>
-      <c r="B31" s="15">
+      <c r="B31" s="21">
         <f>FIXED_COSTS</f>
         <v/>
       </c>
@@ -1751,7 +1802,7 @@
           <t>TOTAL_COST</t>
         </is>
       </c>
-      <c r="B32" s="19">
+      <c r="B32" s="20">
         <f>FERTILIZER_COST+TOTAL_LABOR_COST+FIXED_COSTS</f>
         <v/>
       </c>
@@ -1765,7 +1816,7 @@
           <t>SEASON_PROFIT</t>
         </is>
       </c>
-      <c r="B34" s="20">
+      <c r="B34" s="22">
         <f>SEASON_REVENUE-FERTILIZER_COST-TOTAL_LABOR_COST-FIXED_COSTS</f>
         <v/>
       </c>
@@ -1880,137 +1931,137 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>q</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Labor hours</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>Labor cost</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>Fertilizer</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E6" s="23" t="inlineStr">
         <is>
           <t>Total cost</t>
         </is>
       </c>
-      <c r="F6" s="21" t="inlineStr">
+      <c r="F6" s="23" t="inlineStr">
         <is>
           <t>Marginal cost</t>
         </is>
       </c>
-      <c r="G6" s="21" t="inlineStr">
+      <c r="G6" s="23" t="inlineStr">
         <is>
           <t>Price per bed</t>
         </is>
       </c>
-      <c r="H6" s="21" t="inlineStr">
+      <c r="H6" s="23" t="inlineStr">
         <is>
           <t>MC &lt;= P</t>
         </is>
       </c>
-      <c r="I6" s="21" t="inlineStr">
+      <c r="I6" s="23" t="inlineStr">
         <is>
           <t>Run of MC &lt;= P</t>
         </is>
       </c>
-      <c r="K6" s="21" t="inlineStr">
+      <c r="K6" s="23" t="inlineStr">
         <is>
           <t>q</t>
         </is>
       </c>
-      <c r="L6" s="21" t="inlineStr">
+      <c r="L6" s="23" t="inlineStr">
         <is>
           <t>Labor hours</t>
         </is>
       </c>
-      <c r="M6" s="21" t="inlineStr">
+      <c r="M6" s="23" t="inlineStr">
         <is>
           <t>Labor cost</t>
         </is>
       </c>
-      <c r="N6" s="21" t="inlineStr">
+      <c r="N6" s="23" t="inlineStr">
         <is>
           <t>Fertilizer</t>
         </is>
       </c>
-      <c r="O6" s="21" t="inlineStr">
+      <c r="O6" s="23" t="inlineStr">
         <is>
           <t>Total cost</t>
         </is>
       </c>
-      <c r="P6" s="21" t="inlineStr">
+      <c r="P6" s="23" t="inlineStr">
         <is>
           <t>Marginal cost</t>
         </is>
       </c>
-      <c r="Q6" s="21" t="inlineStr">
+      <c r="Q6" s="23" t="inlineStr">
         <is>
           <t>Price per bed</t>
         </is>
       </c>
-      <c r="R6" s="21" t="inlineStr">
+      <c r="R6" s="23" t="inlineStr">
         <is>
           <t>MC &lt;= P</t>
         </is>
       </c>
-      <c r="S6" s="21" t="inlineStr">
+      <c r="S6" s="23" t="inlineStr">
         <is>
           <t>Run of MC &lt;= P</t>
         </is>
       </c>
-      <c r="U6" s="21" t="inlineStr">
+      <c r="U6" s="23" t="inlineStr">
         <is>
           <t>q</t>
         </is>
       </c>
-      <c r="V6" s="21" t="inlineStr">
+      <c r="V6" s="23" t="inlineStr">
         <is>
           <t>Labor hours</t>
         </is>
       </c>
-      <c r="W6" s="21" t="inlineStr">
+      <c r="W6" s="23" t="inlineStr">
         <is>
           <t>Labor cost</t>
         </is>
       </c>
-      <c r="X6" s="21" t="inlineStr">
+      <c r="X6" s="23" t="inlineStr">
         <is>
           <t>Fertilizer</t>
         </is>
       </c>
-      <c r="Y6" s="21" t="inlineStr">
+      <c r="Y6" s="23" t="inlineStr">
         <is>
           <t>Total cost</t>
         </is>
       </c>
-      <c r="Z6" s="21" t="inlineStr">
+      <c r="Z6" s="23" t="inlineStr">
         <is>
           <t>Marginal cost</t>
         </is>
       </c>
-      <c r="AA6" s="21" t="inlineStr">
+      <c r="AA6" s="23" t="inlineStr">
         <is>
           <t>Price per bed</t>
         </is>
       </c>
-      <c r="AB6" s="21" t="inlineStr">
+      <c r="AB6" s="23" t="inlineStr">
         <is>
           <t>MC &lt;= P</t>
         </is>
       </c>
-      <c r="AC6" s="21" t="inlineStr">
+      <c r="AC6" s="23" t="inlineStr">
         <is>
           <t>Run of MC &lt;= P</t>
         </is>
@@ -2024,20 +2075,20 @@
         <f>A7*HRS_PER_BED_WEEK_TOM*WEEKS*(1+DIM_PCT_TOM)^A7</f>
         <v/>
       </c>
-      <c r="C7" s="19">
+      <c r="C7" s="20">
         <f>MIN(B7,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,B7-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="20">
         <f>A7*FERTILIZER_PER_BED_TOM</f>
         <v/>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="20">
         <f>C7+D7</f>
         <v/>
       </c>
-      <c r="F7" s="19" t="inlineStr"/>
-      <c r="G7" s="19">
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="20">
         <f>PRICE_PER_BED_TOM</f>
         <v/>
       </c>
@@ -2052,20 +2103,20 @@
         <f>K7*HRS_PER_BED_WEEK_CAR*WEEKS*(1+DIM_PCT_CAR)^K7</f>
         <v/>
       </c>
-      <c r="M7" s="19">
+      <c r="M7" s="20">
         <f>MIN(L7,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,L7-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="N7" s="19">
+      <c r="N7" s="20">
         <f>K7*FERTILIZER_PER_BED_CAR</f>
         <v/>
       </c>
-      <c r="O7" s="19">
+      <c r="O7" s="20">
         <f>M7+N7</f>
         <v/>
       </c>
-      <c r="P7" s="19" t="inlineStr"/>
-      <c r="Q7" s="19">
+      <c r="P7" s="20" t="inlineStr"/>
+      <c r="Q7" s="20">
         <f>PRICE_PER_BED_CAR</f>
         <v/>
       </c>
@@ -2080,20 +2131,20 @@
         <f>U7*HRS_PER_BED_WEEK_MES*WEEKS*(1+DIM_PCT_MES)^U7</f>
         <v/>
       </c>
-      <c r="W7" s="19">
+      <c r="W7" s="20">
         <f>MIN(V7,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,V7-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="X7" s="19">
+      <c r="X7" s="20">
         <f>U7*FERTILIZER_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="Y7" s="19">
+      <c r="Y7" s="20">
         <f>W7+X7</f>
         <v/>
       </c>
-      <c r="Z7" s="19" t="inlineStr"/>
-      <c r="AA7" s="19">
+      <c r="Z7" s="20" t="inlineStr"/>
+      <c r="AA7" s="20">
         <f>PRICE_PER_BED_MES</f>
         <v/>
       </c>
@@ -2110,31 +2161,31 @@
         <f>A8*HRS_PER_BED_WEEK_TOM*WEEKS*(1+DIM_PCT_TOM)^A8</f>
         <v/>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="20">
         <f>MIN(B8,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,B8-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="20">
         <f>A8*FERTILIZER_PER_BED_TOM</f>
         <v/>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="20">
         <f>C8+D8</f>
         <v/>
       </c>
-      <c r="F8" s="19">
+      <c r="F8" s="20">
         <f>E8-E7</f>
         <v/>
       </c>
-      <c r="G8" s="19">
+      <c r="G8" s="20">
         <f>PRICE_PER_BED_TOM</f>
         <v/>
       </c>
-      <c r="H8" s="22">
+      <c r="H8" s="24">
         <f>IF(F8&lt;=PRICE_PER_BED_TOM,1,0)</f>
         <v/>
       </c>
-      <c r="I8" s="22">
+      <c r="I8" s="24">
         <f>I7*H8</f>
         <v/>
       </c>
@@ -2145,31 +2196,31 @@
         <f>K8*HRS_PER_BED_WEEK_CAR*WEEKS*(1+DIM_PCT_CAR)^K8</f>
         <v/>
       </c>
-      <c r="M8" s="19">
+      <c r="M8" s="20">
         <f>MIN(L8,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,L8-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="N8" s="19">
+      <c r="N8" s="20">
         <f>K8*FERTILIZER_PER_BED_CAR</f>
         <v/>
       </c>
-      <c r="O8" s="19">
+      <c r="O8" s="20">
         <f>M8+N8</f>
         <v/>
       </c>
-      <c r="P8" s="19">
+      <c r="P8" s="20">
         <f>O8-O7</f>
         <v/>
       </c>
-      <c r="Q8" s="19">
+      <c r="Q8" s="20">
         <f>PRICE_PER_BED_CAR</f>
         <v/>
       </c>
-      <c r="R8" s="22">
+      <c r="R8" s="24">
         <f>IF(P8&lt;=PRICE_PER_BED_CAR,1,0)</f>
         <v/>
       </c>
-      <c r="S8" s="22">
+      <c r="S8" s="24">
         <f>S7*R8</f>
         <v/>
       </c>
@@ -2180,31 +2231,31 @@
         <f>U8*HRS_PER_BED_WEEK_MES*WEEKS*(1+DIM_PCT_MES)^U8</f>
         <v/>
       </c>
-      <c r="W8" s="19">
+      <c r="W8" s="20">
         <f>MIN(V8,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,V8-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="X8" s="19">
+      <c r="X8" s="20">
         <f>U8*FERTILIZER_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="Y8" s="19">
+      <c r="Y8" s="20">
         <f>W8+X8</f>
         <v/>
       </c>
-      <c r="Z8" s="19">
+      <c r="Z8" s="20">
         <f>Y8-Y7</f>
         <v/>
       </c>
-      <c r="AA8" s="19">
+      <c r="AA8" s="20">
         <f>PRICE_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="AB8" s="22">
+      <c r="AB8" s="24">
         <f>IF(Z8&lt;=PRICE_PER_BED_MES,1,0)</f>
         <v/>
       </c>
-      <c r="AC8" s="22">
+      <c r="AC8" s="24">
         <f>AC7*AB8</f>
         <v/>
       </c>
@@ -2217,31 +2268,31 @@
         <f>A9*HRS_PER_BED_WEEK_TOM*WEEKS*(1+DIM_PCT_TOM)^A9</f>
         <v/>
       </c>
-      <c r="C9" s="19">
+      <c r="C9" s="20">
         <f>MIN(B9,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,B9-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="20">
         <f>A9*FERTILIZER_PER_BED_TOM</f>
         <v/>
       </c>
-      <c r="E9" s="19">
+      <c r="E9" s="20">
         <f>C9+D9</f>
         <v/>
       </c>
-      <c r="F9" s="19">
+      <c r="F9" s="20">
         <f>E9-E8</f>
         <v/>
       </c>
-      <c r="G9" s="19">
+      <c r="G9" s="20">
         <f>PRICE_PER_BED_TOM</f>
         <v/>
       </c>
-      <c r="H9" s="22">
+      <c r="H9" s="24">
         <f>IF(F9&lt;=PRICE_PER_BED_TOM,1,0)</f>
         <v/>
       </c>
-      <c r="I9" s="22">
+      <c r="I9" s="24">
         <f>I8*H9</f>
         <v/>
       </c>
@@ -2252,31 +2303,31 @@
         <f>K9*HRS_PER_BED_WEEK_CAR*WEEKS*(1+DIM_PCT_CAR)^K9</f>
         <v/>
       </c>
-      <c r="M9" s="19">
+      <c r="M9" s="20">
         <f>MIN(L9,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,L9-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="N9" s="19">
+      <c r="N9" s="20">
         <f>K9*FERTILIZER_PER_BED_CAR</f>
         <v/>
       </c>
-      <c r="O9" s="19">
+      <c r="O9" s="20">
         <f>M9+N9</f>
         <v/>
       </c>
-      <c r="P9" s="19">
+      <c r="P9" s="20">
         <f>O9-O8</f>
         <v/>
       </c>
-      <c r="Q9" s="19">
+      <c r="Q9" s="20">
         <f>PRICE_PER_BED_CAR</f>
         <v/>
       </c>
-      <c r="R9" s="22">
+      <c r="R9" s="24">
         <f>IF(P9&lt;=PRICE_PER_BED_CAR,1,0)</f>
         <v/>
       </c>
-      <c r="S9" s="22">
+      <c r="S9" s="24">
         <f>S8*R9</f>
         <v/>
       </c>
@@ -2287,31 +2338,31 @@
         <f>U9*HRS_PER_BED_WEEK_MES*WEEKS*(1+DIM_PCT_MES)^U9</f>
         <v/>
       </c>
-      <c r="W9" s="19">
+      <c r="W9" s="20">
         <f>MIN(V9,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,V9-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="X9" s="19">
+      <c r="X9" s="20">
         <f>U9*FERTILIZER_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="Y9" s="19">
+      <c r="Y9" s="20">
         <f>W9+X9</f>
         <v/>
       </c>
-      <c r="Z9" s="19">
+      <c r="Z9" s="20">
         <f>Y9-Y8</f>
         <v/>
       </c>
-      <c r="AA9" s="19">
+      <c r="AA9" s="20">
         <f>PRICE_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="AB9" s="22">
+      <c r="AB9" s="24">
         <f>IF(Z9&lt;=PRICE_PER_BED_MES,1,0)</f>
         <v/>
       </c>
-      <c r="AC9" s="22">
+      <c r="AC9" s="24">
         <f>AC8*AB9</f>
         <v/>
       </c>
@@ -2324,31 +2375,31 @@
         <f>A10*HRS_PER_BED_WEEK_TOM*WEEKS*(1+DIM_PCT_TOM)^A10</f>
         <v/>
       </c>
-      <c r="C10" s="19">
+      <c r="C10" s="20">
         <f>MIN(B10,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,B10-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="20">
         <f>A10*FERTILIZER_PER_BED_TOM</f>
         <v/>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="20">
         <f>C10+D10</f>
         <v/>
       </c>
-      <c r="F10" s="19">
+      <c r="F10" s="20">
         <f>E10-E9</f>
         <v/>
       </c>
-      <c r="G10" s="19">
+      <c r="G10" s="20">
         <f>PRICE_PER_BED_TOM</f>
         <v/>
       </c>
-      <c r="H10" s="22">
+      <c r="H10" s="24">
         <f>IF(F10&lt;=PRICE_PER_BED_TOM,1,0)</f>
         <v/>
       </c>
-      <c r="I10" s="22">
+      <c r="I10" s="24">
         <f>I9*H10</f>
         <v/>
       </c>
@@ -2359,31 +2410,31 @@
         <f>K10*HRS_PER_BED_WEEK_CAR*WEEKS*(1+DIM_PCT_CAR)^K10</f>
         <v/>
       </c>
-      <c r="M10" s="19">
+      <c r="M10" s="20">
         <f>MIN(L10,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,L10-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="N10" s="19">
+      <c r="N10" s="20">
         <f>K10*FERTILIZER_PER_BED_CAR</f>
         <v/>
       </c>
-      <c r="O10" s="19">
+      <c r="O10" s="20">
         <f>M10+N10</f>
         <v/>
       </c>
-      <c r="P10" s="19">
+      <c r="P10" s="20">
         <f>O10-O9</f>
         <v/>
       </c>
-      <c r="Q10" s="19">
+      <c r="Q10" s="20">
         <f>PRICE_PER_BED_CAR</f>
         <v/>
       </c>
-      <c r="R10" s="22">
+      <c r="R10" s="24">
         <f>IF(P10&lt;=PRICE_PER_BED_CAR,1,0)</f>
         <v/>
       </c>
-      <c r="S10" s="22">
+      <c r="S10" s="24">
         <f>S9*R10</f>
         <v/>
       </c>
@@ -2394,31 +2445,31 @@
         <f>U10*HRS_PER_BED_WEEK_MES*WEEKS*(1+DIM_PCT_MES)^U10</f>
         <v/>
       </c>
-      <c r="W10" s="19">
+      <c r="W10" s="20">
         <f>MIN(V10,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,V10-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="X10" s="19">
+      <c r="X10" s="20">
         <f>U10*FERTILIZER_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="Y10" s="19">
+      <c r="Y10" s="20">
         <f>W10+X10</f>
         <v/>
       </c>
-      <c r="Z10" s="19">
+      <c r="Z10" s="20">
         <f>Y10-Y9</f>
         <v/>
       </c>
-      <c r="AA10" s="19">
+      <c r="AA10" s="20">
         <f>PRICE_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="AB10" s="22">
+      <c r="AB10" s="24">
         <f>IF(Z10&lt;=PRICE_PER_BED_MES,1,0)</f>
         <v/>
       </c>
-      <c r="AC10" s="22">
+      <c r="AC10" s="24">
         <f>AC9*AB10</f>
         <v/>
       </c>
@@ -2431,31 +2482,31 @@
         <f>A11*HRS_PER_BED_WEEK_TOM*WEEKS*(1+DIM_PCT_TOM)^A11</f>
         <v/>
       </c>
-      <c r="C11" s="19">
+      <c r="C11" s="20">
         <f>MIN(B11,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,B11-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="20">
         <f>A11*FERTILIZER_PER_BED_TOM</f>
         <v/>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="20">
         <f>C11+D11</f>
         <v/>
       </c>
-      <c r="F11" s="19">
+      <c r="F11" s="20">
         <f>E11-E10</f>
         <v/>
       </c>
-      <c r="G11" s="19">
+      <c r="G11" s="20">
         <f>PRICE_PER_BED_TOM</f>
         <v/>
       </c>
-      <c r="H11" s="22">
+      <c r="H11" s="24">
         <f>IF(F11&lt;=PRICE_PER_BED_TOM,1,0)</f>
         <v/>
       </c>
-      <c r="I11" s="22">
+      <c r="I11" s="24">
         <f>I10*H11</f>
         <v/>
       </c>
@@ -2466,31 +2517,31 @@
         <f>K11*HRS_PER_BED_WEEK_CAR*WEEKS*(1+DIM_PCT_CAR)^K11</f>
         <v/>
       </c>
-      <c r="M11" s="19">
+      <c r="M11" s="20">
         <f>MIN(L11,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,L11-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="N11" s="19">
+      <c r="N11" s="20">
         <f>K11*FERTILIZER_PER_BED_CAR</f>
         <v/>
       </c>
-      <c r="O11" s="19">
+      <c r="O11" s="20">
         <f>M11+N11</f>
         <v/>
       </c>
-      <c r="P11" s="19">
+      <c r="P11" s="20">
         <f>O11-O10</f>
         <v/>
       </c>
-      <c r="Q11" s="19">
+      <c r="Q11" s="20">
         <f>PRICE_PER_BED_CAR</f>
         <v/>
       </c>
-      <c r="R11" s="22">
+      <c r="R11" s="24">
         <f>IF(P11&lt;=PRICE_PER_BED_CAR,1,0)</f>
         <v/>
       </c>
-      <c r="S11" s="22">
+      <c r="S11" s="24">
         <f>S10*R11</f>
         <v/>
       </c>
@@ -2501,31 +2552,31 @@
         <f>U11*HRS_PER_BED_WEEK_MES*WEEKS*(1+DIM_PCT_MES)^U11</f>
         <v/>
       </c>
-      <c r="W11" s="19">
+      <c r="W11" s="20">
         <f>MIN(V11,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,V11-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="X11" s="19">
+      <c r="X11" s="20">
         <f>U11*FERTILIZER_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="Y11" s="19">
+      <c r="Y11" s="20">
         <f>W11+X11</f>
         <v/>
       </c>
-      <c r="Z11" s="19">
+      <c r="Z11" s="20">
         <f>Y11-Y10</f>
         <v/>
       </c>
-      <c r="AA11" s="19">
+      <c r="AA11" s="20">
         <f>PRICE_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="AB11" s="22">
+      <c r="AB11" s="24">
         <f>IF(Z11&lt;=PRICE_PER_BED_MES,1,0)</f>
         <v/>
       </c>
-      <c r="AC11" s="22">
+      <c r="AC11" s="24">
         <f>AC10*AB11</f>
         <v/>
       </c>
@@ -2538,31 +2589,31 @@
         <f>A12*HRS_PER_BED_WEEK_TOM*WEEKS*(1+DIM_PCT_TOM)^A12</f>
         <v/>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="20">
         <f>MIN(B12,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,B12-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="20">
         <f>A12*FERTILIZER_PER_BED_TOM</f>
         <v/>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="20">
         <f>C12+D12</f>
         <v/>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="20">
         <f>E12-E11</f>
         <v/>
       </c>
-      <c r="G12" s="19">
+      <c r="G12" s="20">
         <f>PRICE_PER_BED_TOM</f>
         <v/>
       </c>
-      <c r="H12" s="22">
+      <c r="H12" s="24">
         <f>IF(F12&lt;=PRICE_PER_BED_TOM,1,0)</f>
         <v/>
       </c>
-      <c r="I12" s="22">
+      <c r="I12" s="24">
         <f>I11*H12</f>
         <v/>
       </c>
@@ -2573,31 +2624,31 @@
         <f>K12*HRS_PER_BED_WEEK_CAR*WEEKS*(1+DIM_PCT_CAR)^K12</f>
         <v/>
       </c>
-      <c r="M12" s="19">
+      <c r="M12" s="20">
         <f>MIN(L12,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,L12-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="N12" s="19">
+      <c r="N12" s="20">
         <f>K12*FERTILIZER_PER_BED_CAR</f>
         <v/>
       </c>
-      <c r="O12" s="19">
+      <c r="O12" s="20">
         <f>M12+N12</f>
         <v/>
       </c>
-      <c r="P12" s="19">
+      <c r="P12" s="20">
         <f>O12-O11</f>
         <v/>
       </c>
-      <c r="Q12" s="19">
+      <c r="Q12" s="20">
         <f>PRICE_PER_BED_CAR</f>
         <v/>
       </c>
-      <c r="R12" s="22">
+      <c r="R12" s="24">
         <f>IF(P12&lt;=PRICE_PER_BED_CAR,1,0)</f>
         <v/>
       </c>
-      <c r="S12" s="22">
+      <c r="S12" s="24">
         <f>S11*R12</f>
         <v/>
       </c>
@@ -2608,31 +2659,31 @@
         <f>U12*HRS_PER_BED_WEEK_MES*WEEKS*(1+DIM_PCT_MES)^U12</f>
         <v/>
       </c>
-      <c r="W12" s="19">
+      <c r="W12" s="20">
         <f>MIN(V12,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,V12-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="X12" s="19">
+      <c r="X12" s="20">
         <f>U12*FERTILIZER_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="Y12" s="19">
+      <c r="Y12" s="20">
         <f>W12+X12</f>
         <v/>
       </c>
-      <c r="Z12" s="19">
+      <c r="Z12" s="20">
         <f>Y12-Y11</f>
         <v/>
       </c>
-      <c r="AA12" s="19">
+      <c r="AA12" s="20">
         <f>PRICE_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="AB12" s="22">
+      <c r="AB12" s="24">
         <f>IF(Z12&lt;=PRICE_PER_BED_MES,1,0)</f>
         <v/>
       </c>
-      <c r="AC12" s="22">
+      <c r="AC12" s="24">
         <f>AC11*AB12</f>
         <v/>
       </c>
@@ -2645,31 +2696,31 @@
         <f>A13*HRS_PER_BED_WEEK_TOM*WEEKS*(1+DIM_PCT_TOM)^A13</f>
         <v/>
       </c>
-      <c r="C13" s="19">
+      <c r="C13" s="20">
         <f>MIN(B13,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,B13-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="20">
         <f>A13*FERTILIZER_PER_BED_TOM</f>
         <v/>
       </c>
-      <c r="E13" s="19">
+      <c r="E13" s="20">
         <f>C13+D13</f>
         <v/>
       </c>
-      <c r="F13" s="19">
+      <c r="F13" s="20">
         <f>E13-E12</f>
         <v/>
       </c>
-      <c r="G13" s="19">
+      <c r="G13" s="20">
         <f>PRICE_PER_BED_TOM</f>
         <v/>
       </c>
-      <c r="H13" s="22">
+      <c r="H13" s="24">
         <f>IF(F13&lt;=PRICE_PER_BED_TOM,1,0)</f>
         <v/>
       </c>
-      <c r="I13" s="22">
+      <c r="I13" s="24">
         <f>I12*H13</f>
         <v/>
       </c>
@@ -2680,31 +2731,31 @@
         <f>K13*HRS_PER_BED_WEEK_CAR*WEEKS*(1+DIM_PCT_CAR)^K13</f>
         <v/>
       </c>
-      <c r="M13" s="19">
+      <c r="M13" s="20">
         <f>MIN(L13,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,L13-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="N13" s="19">
+      <c r="N13" s="20">
         <f>K13*FERTILIZER_PER_BED_CAR</f>
         <v/>
       </c>
-      <c r="O13" s="19">
+      <c r="O13" s="20">
         <f>M13+N13</f>
         <v/>
       </c>
-      <c r="P13" s="19">
+      <c r="P13" s="20">
         <f>O13-O12</f>
         <v/>
       </c>
-      <c r="Q13" s="19">
+      <c r="Q13" s="20">
         <f>PRICE_PER_BED_CAR</f>
         <v/>
       </c>
-      <c r="R13" s="22">
+      <c r="R13" s="24">
         <f>IF(P13&lt;=PRICE_PER_BED_CAR,1,0)</f>
         <v/>
       </c>
-      <c r="S13" s="22">
+      <c r="S13" s="24">
         <f>S12*R13</f>
         <v/>
       </c>
@@ -2715,31 +2766,31 @@
         <f>U13*HRS_PER_BED_WEEK_MES*WEEKS*(1+DIM_PCT_MES)^U13</f>
         <v/>
       </c>
-      <c r="W13" s="19">
+      <c r="W13" s="20">
         <f>MIN(V13,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,V13-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="X13" s="19">
+      <c r="X13" s="20">
         <f>U13*FERTILIZER_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="Y13" s="19">
+      <c r="Y13" s="20">
         <f>W13+X13</f>
         <v/>
       </c>
-      <c r="Z13" s="19">
+      <c r="Z13" s="20">
         <f>Y13-Y12</f>
         <v/>
       </c>
-      <c r="AA13" s="19">
+      <c r="AA13" s="20">
         <f>PRICE_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="AB13" s="22">
+      <c r="AB13" s="24">
         <f>IF(Z13&lt;=PRICE_PER_BED_MES,1,0)</f>
         <v/>
       </c>
-      <c r="AC13" s="22">
+      <c r="AC13" s="24">
         <f>AC12*AB13</f>
         <v/>
       </c>
@@ -2752,31 +2803,31 @@
         <f>A14*HRS_PER_BED_WEEK_TOM*WEEKS*(1+DIM_PCT_TOM)^A14</f>
         <v/>
       </c>
-      <c r="C14" s="19">
+      <c r="C14" s="20">
         <f>MIN(B14,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,B14-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="20">
         <f>A14*FERTILIZER_PER_BED_TOM</f>
         <v/>
       </c>
-      <c r="E14" s="19">
+      <c r="E14" s="20">
         <f>C14+D14</f>
         <v/>
       </c>
-      <c r="F14" s="19">
+      <c r="F14" s="20">
         <f>E14-E13</f>
         <v/>
       </c>
-      <c r="G14" s="19">
+      <c r="G14" s="20">
         <f>PRICE_PER_BED_TOM</f>
         <v/>
       </c>
-      <c r="H14" s="22">
+      <c r="H14" s="24">
         <f>IF(F14&lt;=PRICE_PER_BED_TOM,1,0)</f>
         <v/>
       </c>
-      <c r="I14" s="22">
+      <c r="I14" s="24">
         <f>I13*H14</f>
         <v/>
       </c>
@@ -2787,31 +2838,31 @@
         <f>K14*HRS_PER_BED_WEEK_CAR*WEEKS*(1+DIM_PCT_CAR)^K14</f>
         <v/>
       </c>
-      <c r="M14" s="19">
+      <c r="M14" s="20">
         <f>MIN(L14,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,L14-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="N14" s="19">
+      <c r="N14" s="20">
         <f>K14*FERTILIZER_PER_BED_CAR</f>
         <v/>
       </c>
-      <c r="O14" s="19">
+      <c r="O14" s="20">
         <f>M14+N14</f>
         <v/>
       </c>
-      <c r="P14" s="19">
+      <c r="P14" s="20">
         <f>O14-O13</f>
         <v/>
       </c>
-      <c r="Q14" s="19">
+      <c r="Q14" s="20">
         <f>PRICE_PER_BED_CAR</f>
         <v/>
       </c>
-      <c r="R14" s="22">
+      <c r="R14" s="24">
         <f>IF(P14&lt;=PRICE_PER_BED_CAR,1,0)</f>
         <v/>
       </c>
-      <c r="S14" s="22">
+      <c r="S14" s="24">
         <f>S13*R14</f>
         <v/>
       </c>
@@ -2822,31 +2873,31 @@
         <f>U14*HRS_PER_BED_WEEK_MES*WEEKS*(1+DIM_PCT_MES)^U14</f>
         <v/>
       </c>
-      <c r="W14" s="19">
+      <c r="W14" s="20">
         <f>MIN(V14,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,V14-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="X14" s="19">
+      <c r="X14" s="20">
         <f>U14*FERTILIZER_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="Y14" s="19">
+      <c r="Y14" s="20">
         <f>W14+X14</f>
         <v/>
       </c>
-      <c r="Z14" s="19">
+      <c r="Z14" s="20">
         <f>Y14-Y13</f>
         <v/>
       </c>
-      <c r="AA14" s="19">
+      <c r="AA14" s="20">
         <f>PRICE_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="AB14" s="22">
+      <c r="AB14" s="24">
         <f>IF(Z14&lt;=PRICE_PER_BED_MES,1,0)</f>
         <v/>
       </c>
-      <c r="AC14" s="22">
+      <c r="AC14" s="24">
         <f>AC13*AB14</f>
         <v/>
       </c>
@@ -2859,31 +2910,31 @@
         <f>A15*HRS_PER_BED_WEEK_TOM*WEEKS*(1+DIM_PCT_TOM)^A15</f>
         <v/>
       </c>
-      <c r="C15" s="19">
+      <c r="C15" s="20">
         <f>MIN(B15,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,B15-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="20">
         <f>A15*FERTILIZER_PER_BED_TOM</f>
         <v/>
       </c>
-      <c r="E15" s="19">
+      <c r="E15" s="20">
         <f>C15+D15</f>
         <v/>
       </c>
-      <c r="F15" s="19">
+      <c r="F15" s="20">
         <f>E15-E14</f>
         <v/>
       </c>
-      <c r="G15" s="19">
+      <c r="G15" s="20">
         <f>PRICE_PER_BED_TOM</f>
         <v/>
       </c>
-      <c r="H15" s="22">
+      <c r="H15" s="24">
         <f>IF(F15&lt;=PRICE_PER_BED_TOM,1,0)</f>
         <v/>
       </c>
-      <c r="I15" s="22">
+      <c r="I15" s="24">
         <f>I14*H15</f>
         <v/>
       </c>
@@ -2894,31 +2945,31 @@
         <f>K15*HRS_PER_BED_WEEK_CAR*WEEKS*(1+DIM_PCT_CAR)^K15</f>
         <v/>
       </c>
-      <c r="M15" s="19">
+      <c r="M15" s="20">
         <f>MIN(L15,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,L15-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="N15" s="19">
+      <c r="N15" s="20">
         <f>K15*FERTILIZER_PER_BED_CAR</f>
         <v/>
       </c>
-      <c r="O15" s="19">
+      <c r="O15" s="20">
         <f>M15+N15</f>
         <v/>
       </c>
-      <c r="P15" s="19">
+      <c r="P15" s="20">
         <f>O15-O14</f>
         <v/>
       </c>
-      <c r="Q15" s="19">
+      <c r="Q15" s="20">
         <f>PRICE_PER_BED_CAR</f>
         <v/>
       </c>
-      <c r="R15" s="22">
+      <c r="R15" s="24">
         <f>IF(P15&lt;=PRICE_PER_BED_CAR,1,0)</f>
         <v/>
       </c>
-      <c r="S15" s="22">
+      <c r="S15" s="24">
         <f>S14*R15</f>
         <v/>
       </c>
@@ -2929,31 +2980,31 @@
         <f>U15*HRS_PER_BED_WEEK_MES*WEEKS*(1+DIM_PCT_MES)^U15</f>
         <v/>
       </c>
-      <c r="W15" s="19">
+      <c r="W15" s="20">
         <f>MIN(V15,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,V15-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="X15" s="19">
+      <c r="X15" s="20">
         <f>U15*FERTILIZER_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="Y15" s="19">
+      <c r="Y15" s="20">
         <f>W15+X15</f>
         <v/>
       </c>
-      <c r="Z15" s="19">
+      <c r="Z15" s="20">
         <f>Y15-Y14</f>
         <v/>
       </c>
-      <c r="AA15" s="19">
+      <c r="AA15" s="20">
         <f>PRICE_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="AB15" s="22">
+      <c r="AB15" s="24">
         <f>IF(Z15&lt;=PRICE_PER_BED_MES,1,0)</f>
         <v/>
       </c>
-      <c r="AC15" s="22">
+      <c r="AC15" s="24">
         <f>AC14*AB15</f>
         <v/>
       </c>
@@ -2966,31 +3017,31 @@
         <f>A16*HRS_PER_BED_WEEK_TOM*WEEKS*(1+DIM_PCT_TOM)^A16</f>
         <v/>
       </c>
-      <c r="C16" s="19">
+      <c r="C16" s="20">
         <f>MIN(B16,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,B16-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="20">
         <f>A16*FERTILIZER_PER_BED_TOM</f>
         <v/>
       </c>
-      <c r="E16" s="19">
+      <c r="E16" s="20">
         <f>C16+D16</f>
         <v/>
       </c>
-      <c r="F16" s="19">
+      <c r="F16" s="20">
         <f>E16-E15</f>
         <v/>
       </c>
-      <c r="G16" s="19">
+      <c r="G16" s="20">
         <f>PRICE_PER_BED_TOM</f>
         <v/>
       </c>
-      <c r="H16" s="22">
+      <c r="H16" s="24">
         <f>IF(F16&lt;=PRICE_PER_BED_TOM,1,0)</f>
         <v/>
       </c>
-      <c r="I16" s="22">
+      <c r="I16" s="24">
         <f>I15*H16</f>
         <v/>
       </c>
@@ -3001,31 +3052,31 @@
         <f>K16*HRS_PER_BED_WEEK_CAR*WEEKS*(1+DIM_PCT_CAR)^K16</f>
         <v/>
       </c>
-      <c r="M16" s="19">
+      <c r="M16" s="20">
         <f>MIN(L16,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,L16-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="N16" s="19">
+      <c r="N16" s="20">
         <f>K16*FERTILIZER_PER_BED_CAR</f>
         <v/>
       </c>
-      <c r="O16" s="19">
+      <c r="O16" s="20">
         <f>M16+N16</f>
         <v/>
       </c>
-      <c r="P16" s="19">
+      <c r="P16" s="20">
         <f>O16-O15</f>
         <v/>
       </c>
-      <c r="Q16" s="19">
+      <c r="Q16" s="20">
         <f>PRICE_PER_BED_CAR</f>
         <v/>
       </c>
-      <c r="R16" s="22">
+      <c r="R16" s="24">
         <f>IF(P16&lt;=PRICE_PER_BED_CAR,1,0)</f>
         <v/>
       </c>
-      <c r="S16" s="22">
+      <c r="S16" s="24">
         <f>S15*R16</f>
         <v/>
       </c>
@@ -3036,31 +3087,31 @@
         <f>U16*HRS_PER_BED_WEEK_MES*WEEKS*(1+DIM_PCT_MES)^U16</f>
         <v/>
       </c>
-      <c r="W16" s="19">
+      <c r="W16" s="20">
         <f>MIN(V16,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,V16-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="X16" s="19">
+      <c r="X16" s="20">
         <f>U16*FERTILIZER_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="Y16" s="19">
+      <c r="Y16" s="20">
         <f>W16+X16</f>
         <v/>
       </c>
-      <c r="Z16" s="19">
+      <c r="Z16" s="20">
         <f>Y16-Y15</f>
         <v/>
       </c>
-      <c r="AA16" s="19">
+      <c r="AA16" s="20">
         <f>PRICE_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="AB16" s="22">
+      <c r="AB16" s="24">
         <f>IF(Z16&lt;=PRICE_PER_BED_MES,1,0)</f>
         <v/>
       </c>
-      <c r="AC16" s="22">
+      <c r="AC16" s="24">
         <f>AC15*AB16</f>
         <v/>
       </c>
@@ -3073,31 +3124,31 @@
         <f>A17*HRS_PER_BED_WEEK_TOM*WEEKS*(1+DIM_PCT_TOM)^A17</f>
         <v/>
       </c>
-      <c r="C17" s="19">
+      <c r="C17" s="20">
         <f>MIN(B17,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,B17-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="20">
         <f>A17*FERTILIZER_PER_BED_TOM</f>
         <v/>
       </c>
-      <c r="E17" s="19">
+      <c r="E17" s="20">
         <f>C17+D17</f>
         <v/>
       </c>
-      <c r="F17" s="19">
+      <c r="F17" s="20">
         <f>E17-E16</f>
         <v/>
       </c>
-      <c r="G17" s="19">
+      <c r="G17" s="20">
         <f>PRICE_PER_BED_TOM</f>
         <v/>
       </c>
-      <c r="H17" s="22">
+      <c r="H17" s="24">
         <f>IF(F17&lt;=PRICE_PER_BED_TOM,1,0)</f>
         <v/>
       </c>
-      <c r="I17" s="22">
+      <c r="I17" s="24">
         <f>I16*H17</f>
         <v/>
       </c>
@@ -3108,31 +3159,31 @@
         <f>K17*HRS_PER_BED_WEEK_CAR*WEEKS*(1+DIM_PCT_CAR)^K17</f>
         <v/>
       </c>
-      <c r="M17" s="19">
+      <c r="M17" s="20">
         <f>MIN(L17,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,L17-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="N17" s="19">
+      <c r="N17" s="20">
         <f>K17*FERTILIZER_PER_BED_CAR</f>
         <v/>
       </c>
-      <c r="O17" s="19">
+      <c r="O17" s="20">
         <f>M17+N17</f>
         <v/>
       </c>
-      <c r="P17" s="19">
+      <c r="P17" s="20">
         <f>O17-O16</f>
         <v/>
       </c>
-      <c r="Q17" s="19">
+      <c r="Q17" s="20">
         <f>PRICE_PER_BED_CAR</f>
         <v/>
       </c>
-      <c r="R17" s="22">
+      <c r="R17" s="24">
         <f>IF(P17&lt;=PRICE_PER_BED_CAR,1,0)</f>
         <v/>
       </c>
-      <c r="S17" s="22">
+      <c r="S17" s="24">
         <f>S16*R17</f>
         <v/>
       </c>
@@ -3143,31 +3194,31 @@
         <f>U17*HRS_PER_BED_WEEK_MES*WEEKS*(1+DIM_PCT_MES)^U17</f>
         <v/>
       </c>
-      <c r="W17" s="19">
+      <c r="W17" s="20">
         <f>MIN(V17,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,V17-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="X17" s="19">
+      <c r="X17" s="20">
         <f>U17*FERTILIZER_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="Y17" s="19">
+      <c r="Y17" s="20">
         <f>W17+X17</f>
         <v/>
       </c>
-      <c r="Z17" s="19">
+      <c r="Z17" s="20">
         <f>Y17-Y16</f>
         <v/>
       </c>
-      <c r="AA17" s="19">
+      <c r="AA17" s="20">
         <f>PRICE_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="AB17" s="22">
+      <c r="AB17" s="24">
         <f>IF(Z17&lt;=PRICE_PER_BED_MES,1,0)</f>
         <v/>
       </c>
-      <c r="AC17" s="22">
+      <c r="AC17" s="24">
         <f>AC16*AB17</f>
         <v/>
       </c>
@@ -3180,31 +3231,31 @@
         <f>A18*HRS_PER_BED_WEEK_TOM*WEEKS*(1+DIM_PCT_TOM)^A18</f>
         <v/>
       </c>
-      <c r="C18" s="19">
+      <c r="C18" s="20">
         <f>MIN(B18,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,B18-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="20">
         <f>A18*FERTILIZER_PER_BED_TOM</f>
         <v/>
       </c>
-      <c r="E18" s="19">
+      <c r="E18" s="20">
         <f>C18+D18</f>
         <v/>
       </c>
-      <c r="F18" s="19">
+      <c r="F18" s="20">
         <f>E18-E17</f>
         <v/>
       </c>
-      <c r="G18" s="19">
+      <c r="G18" s="20">
         <f>PRICE_PER_BED_TOM</f>
         <v/>
       </c>
-      <c r="H18" s="22">
+      <c r="H18" s="24">
         <f>IF(F18&lt;=PRICE_PER_BED_TOM,1,0)</f>
         <v/>
       </c>
-      <c r="I18" s="22">
+      <c r="I18" s="24">
         <f>I17*H18</f>
         <v/>
       </c>
@@ -3215,31 +3266,31 @@
         <f>K18*HRS_PER_BED_WEEK_CAR*WEEKS*(1+DIM_PCT_CAR)^K18</f>
         <v/>
       </c>
-      <c r="M18" s="19">
+      <c r="M18" s="20">
         <f>MIN(L18,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,L18-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="N18" s="19">
+      <c r="N18" s="20">
         <f>K18*FERTILIZER_PER_BED_CAR</f>
         <v/>
       </c>
-      <c r="O18" s="19">
+      <c r="O18" s="20">
         <f>M18+N18</f>
         <v/>
       </c>
-      <c r="P18" s="19">
+      <c r="P18" s="20">
         <f>O18-O17</f>
         <v/>
       </c>
-      <c r="Q18" s="19">
+      <c r="Q18" s="20">
         <f>PRICE_PER_BED_CAR</f>
         <v/>
       </c>
-      <c r="R18" s="22">
+      <c r="R18" s="24">
         <f>IF(P18&lt;=PRICE_PER_BED_CAR,1,0)</f>
         <v/>
       </c>
-      <c r="S18" s="22">
+      <c r="S18" s="24">
         <f>S17*R18</f>
         <v/>
       </c>
@@ -3250,31 +3301,31 @@
         <f>U18*HRS_PER_BED_WEEK_MES*WEEKS*(1+DIM_PCT_MES)^U18</f>
         <v/>
       </c>
-      <c r="W18" s="19">
+      <c r="W18" s="20">
         <f>MIN(V18,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,V18-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="X18" s="19">
+      <c r="X18" s="20">
         <f>U18*FERTILIZER_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="Y18" s="19">
+      <c r="Y18" s="20">
         <f>W18+X18</f>
         <v/>
       </c>
-      <c r="Z18" s="19">
+      <c r="Z18" s="20">
         <f>Y18-Y17</f>
         <v/>
       </c>
-      <c r="AA18" s="19">
+      <c r="AA18" s="20">
         <f>PRICE_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="AB18" s="22">
+      <c r="AB18" s="24">
         <f>IF(Z18&lt;=PRICE_PER_BED_MES,1,0)</f>
         <v/>
       </c>
-      <c r="AC18" s="22">
+      <c r="AC18" s="24">
         <f>AC17*AB18</f>
         <v/>
       </c>
@@ -3287,31 +3338,31 @@
         <f>A19*HRS_PER_BED_WEEK_TOM*WEEKS*(1+DIM_PCT_TOM)^A19</f>
         <v/>
       </c>
-      <c r="C19" s="19">
+      <c r="C19" s="20">
         <f>MIN(B19,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,B19-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="20">
         <f>A19*FERTILIZER_PER_BED_TOM</f>
         <v/>
       </c>
-      <c r="E19" s="19">
+      <c r="E19" s="20">
         <f>C19+D19</f>
         <v/>
       </c>
-      <c r="F19" s="19">
+      <c r="F19" s="20">
         <f>E19-E18</f>
         <v/>
       </c>
-      <c r="G19" s="19">
+      <c r="G19" s="20">
         <f>PRICE_PER_BED_TOM</f>
         <v/>
       </c>
-      <c r="H19" s="22">
+      <c r="H19" s="24">
         <f>IF(F19&lt;=PRICE_PER_BED_TOM,1,0)</f>
         <v/>
       </c>
-      <c r="I19" s="22">
+      <c r="I19" s="24">
         <f>I18*H19</f>
         <v/>
       </c>
@@ -3322,31 +3373,31 @@
         <f>K19*HRS_PER_BED_WEEK_CAR*WEEKS*(1+DIM_PCT_CAR)^K19</f>
         <v/>
       </c>
-      <c r="M19" s="19">
+      <c r="M19" s="20">
         <f>MIN(L19,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,L19-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="N19" s="19">
+      <c r="N19" s="20">
         <f>K19*FERTILIZER_PER_BED_CAR</f>
         <v/>
       </c>
-      <c r="O19" s="19">
+      <c r="O19" s="20">
         <f>M19+N19</f>
         <v/>
       </c>
-      <c r="P19" s="19">
+      <c r="P19" s="20">
         <f>O19-O18</f>
         <v/>
       </c>
-      <c r="Q19" s="19">
+      <c r="Q19" s="20">
         <f>PRICE_PER_BED_CAR</f>
         <v/>
       </c>
-      <c r="R19" s="22">
+      <c r="R19" s="24">
         <f>IF(P19&lt;=PRICE_PER_BED_CAR,1,0)</f>
         <v/>
       </c>
-      <c r="S19" s="22">
+      <c r="S19" s="24">
         <f>S18*R19</f>
         <v/>
       </c>
@@ -3357,31 +3408,31 @@
         <f>U19*HRS_PER_BED_WEEK_MES*WEEKS*(1+DIM_PCT_MES)^U19</f>
         <v/>
       </c>
-      <c r="W19" s="19">
+      <c r="W19" s="20">
         <f>MIN(V19,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,V19-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="X19" s="19">
+      <c r="X19" s="20">
         <f>U19*FERTILIZER_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="Y19" s="19">
+      <c r="Y19" s="20">
         <f>W19+X19</f>
         <v/>
       </c>
-      <c r="Z19" s="19">
+      <c r="Z19" s="20">
         <f>Y19-Y18</f>
         <v/>
       </c>
-      <c r="AA19" s="19">
+      <c r="AA19" s="20">
         <f>PRICE_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="AB19" s="22">
+      <c r="AB19" s="24">
         <f>IF(Z19&lt;=PRICE_PER_BED_MES,1,0)</f>
         <v/>
       </c>
-      <c r="AC19" s="22">
+      <c r="AC19" s="24">
         <f>AC18*AB19</f>
         <v/>
       </c>
@@ -3394,31 +3445,31 @@
         <f>A20*HRS_PER_BED_WEEK_TOM*WEEKS*(1+DIM_PCT_TOM)^A20</f>
         <v/>
       </c>
-      <c r="C20" s="19">
+      <c r="C20" s="20">
         <f>MIN(B20,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,B20-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="20">
         <f>A20*FERTILIZER_PER_BED_TOM</f>
         <v/>
       </c>
-      <c r="E20" s="19">
+      <c r="E20" s="20">
         <f>C20+D20</f>
         <v/>
       </c>
-      <c r="F20" s="19">
+      <c r="F20" s="20">
         <f>E20-E19</f>
         <v/>
       </c>
-      <c r="G20" s="19">
+      <c r="G20" s="20">
         <f>PRICE_PER_BED_TOM</f>
         <v/>
       </c>
-      <c r="H20" s="22">
+      <c r="H20" s="24">
         <f>IF(F20&lt;=PRICE_PER_BED_TOM,1,0)</f>
         <v/>
       </c>
-      <c r="I20" s="22">
+      <c r="I20" s="24">
         <f>I19*H20</f>
         <v/>
       </c>
@@ -3429,31 +3480,31 @@
         <f>K20*HRS_PER_BED_WEEK_CAR*WEEKS*(1+DIM_PCT_CAR)^K20</f>
         <v/>
       </c>
-      <c r="M20" s="19">
+      <c r="M20" s="20">
         <f>MIN(L20,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,L20-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="N20" s="19">
+      <c r="N20" s="20">
         <f>K20*FERTILIZER_PER_BED_CAR</f>
         <v/>
       </c>
-      <c r="O20" s="19">
+      <c r="O20" s="20">
         <f>M20+N20</f>
         <v/>
       </c>
-      <c r="P20" s="19">
+      <c r="P20" s="20">
         <f>O20-O19</f>
         <v/>
       </c>
-      <c r="Q20" s="19">
+      <c r="Q20" s="20">
         <f>PRICE_PER_BED_CAR</f>
         <v/>
       </c>
-      <c r="R20" s="22">
+      <c r="R20" s="24">
         <f>IF(P20&lt;=PRICE_PER_BED_CAR,1,0)</f>
         <v/>
       </c>
-      <c r="S20" s="22">
+      <c r="S20" s="24">
         <f>S19*R20</f>
         <v/>
       </c>
@@ -3464,31 +3515,31 @@
         <f>U20*HRS_PER_BED_WEEK_MES*WEEKS*(1+DIM_PCT_MES)^U20</f>
         <v/>
       </c>
-      <c r="W20" s="19">
+      <c r="W20" s="20">
         <f>MIN(V20,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,V20-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="X20" s="19">
+      <c r="X20" s="20">
         <f>U20*FERTILIZER_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="Y20" s="19">
+      <c r="Y20" s="20">
         <f>W20+X20</f>
         <v/>
       </c>
-      <c r="Z20" s="19">
+      <c r="Z20" s="20">
         <f>Y20-Y19</f>
         <v/>
       </c>
-      <c r="AA20" s="19">
+      <c r="AA20" s="20">
         <f>PRICE_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="AB20" s="22">
+      <c r="AB20" s="24">
         <f>IF(Z20&lt;=PRICE_PER_BED_MES,1,0)</f>
         <v/>
       </c>
-      <c r="AC20" s="22">
+      <c r="AC20" s="24">
         <f>AC19*AB20</f>
         <v/>
       </c>
@@ -3501,31 +3552,31 @@
         <f>A21*HRS_PER_BED_WEEK_TOM*WEEKS*(1+DIM_PCT_TOM)^A21</f>
         <v/>
       </c>
-      <c r="C21" s="19">
+      <c r="C21" s="20">
         <f>MIN(B21,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,B21-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="20">
         <f>A21*FERTILIZER_PER_BED_TOM</f>
         <v/>
       </c>
-      <c r="E21" s="19">
+      <c r="E21" s="20">
         <f>C21+D21</f>
         <v/>
       </c>
-      <c r="F21" s="19">
+      <c r="F21" s="20">
         <f>E21-E20</f>
         <v/>
       </c>
-      <c r="G21" s="19">
+      <c r="G21" s="20">
         <f>PRICE_PER_BED_TOM</f>
         <v/>
       </c>
-      <c r="H21" s="22">
+      <c r="H21" s="24">
         <f>IF(F21&lt;=PRICE_PER_BED_TOM,1,0)</f>
         <v/>
       </c>
-      <c r="I21" s="22">
+      <c r="I21" s="24">
         <f>I20*H21</f>
         <v/>
       </c>
@@ -3536,31 +3587,31 @@
         <f>K21*HRS_PER_BED_WEEK_CAR*WEEKS*(1+DIM_PCT_CAR)^K21</f>
         <v/>
       </c>
-      <c r="M21" s="19">
+      <c r="M21" s="20">
         <f>MIN(L21,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,L21-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="N21" s="19">
+      <c r="N21" s="20">
         <f>K21*FERTILIZER_PER_BED_CAR</f>
         <v/>
       </c>
-      <c r="O21" s="19">
+      <c r="O21" s="20">
         <f>M21+N21</f>
         <v/>
       </c>
-      <c r="P21" s="19">
+      <c r="P21" s="20">
         <f>O21-O20</f>
         <v/>
       </c>
-      <c r="Q21" s="19">
+      <c r="Q21" s="20">
         <f>PRICE_PER_BED_CAR</f>
         <v/>
       </c>
-      <c r="R21" s="22">
+      <c r="R21" s="24">
         <f>IF(P21&lt;=PRICE_PER_BED_CAR,1,0)</f>
         <v/>
       </c>
-      <c r="S21" s="22">
+      <c r="S21" s="24">
         <f>S20*R21</f>
         <v/>
       </c>
@@ -3571,31 +3622,31 @@
         <f>U21*HRS_PER_BED_WEEK_MES*WEEKS*(1+DIM_PCT_MES)^U21</f>
         <v/>
       </c>
-      <c r="W21" s="19">
+      <c r="W21" s="20">
         <f>MIN(V21,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,V21-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="X21" s="19">
+      <c r="X21" s="20">
         <f>U21*FERTILIZER_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="Y21" s="19">
+      <c r="Y21" s="20">
         <f>W21+X21</f>
         <v/>
       </c>
-      <c r="Z21" s="19">
+      <c r="Z21" s="20">
         <f>Y21-Y20</f>
         <v/>
       </c>
-      <c r="AA21" s="19">
+      <c r="AA21" s="20">
         <f>PRICE_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="AB21" s="22">
+      <c r="AB21" s="24">
         <f>IF(Z21&lt;=PRICE_PER_BED_MES,1,0)</f>
         <v/>
       </c>
-      <c r="AC21" s="22">
+      <c r="AC21" s="24">
         <f>AC20*AB21</f>
         <v/>
       </c>
@@ -3608,31 +3659,31 @@
         <f>A22*HRS_PER_BED_WEEK_TOM*WEEKS*(1+DIM_PCT_TOM)^A22</f>
         <v/>
       </c>
-      <c r="C22" s="19">
+      <c r="C22" s="20">
         <f>MIN(B22,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,B22-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="20">
         <f>A22*FERTILIZER_PER_BED_TOM</f>
         <v/>
       </c>
-      <c r="E22" s="19">
+      <c r="E22" s="20">
         <f>C22+D22</f>
         <v/>
       </c>
-      <c r="F22" s="19">
+      <c r="F22" s="20">
         <f>E22-E21</f>
         <v/>
       </c>
-      <c r="G22" s="19">
+      <c r="G22" s="20">
         <f>PRICE_PER_BED_TOM</f>
         <v/>
       </c>
-      <c r="H22" s="22">
+      <c r="H22" s="24">
         <f>IF(F22&lt;=PRICE_PER_BED_TOM,1,0)</f>
         <v/>
       </c>
-      <c r="I22" s="22">
+      <c r="I22" s="24">
         <f>I21*H22</f>
         <v/>
       </c>
@@ -3643,31 +3694,31 @@
         <f>K22*HRS_PER_BED_WEEK_CAR*WEEKS*(1+DIM_PCT_CAR)^K22</f>
         <v/>
       </c>
-      <c r="M22" s="19">
+      <c r="M22" s="20">
         <f>MIN(L22,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,L22-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="N22" s="19">
+      <c r="N22" s="20">
         <f>K22*FERTILIZER_PER_BED_CAR</f>
         <v/>
       </c>
-      <c r="O22" s="19">
+      <c r="O22" s="20">
         <f>M22+N22</f>
         <v/>
       </c>
-      <c r="P22" s="19">
+      <c r="P22" s="20">
         <f>O22-O21</f>
         <v/>
       </c>
-      <c r="Q22" s="19">
+      <c r="Q22" s="20">
         <f>PRICE_PER_BED_CAR</f>
         <v/>
       </c>
-      <c r="R22" s="22">
+      <c r="R22" s="24">
         <f>IF(P22&lt;=PRICE_PER_BED_CAR,1,0)</f>
         <v/>
       </c>
-      <c r="S22" s="22">
+      <c r="S22" s="24">
         <f>S21*R22</f>
         <v/>
       </c>
@@ -3678,31 +3729,31 @@
         <f>U22*HRS_PER_BED_WEEK_MES*WEEKS*(1+DIM_PCT_MES)^U22</f>
         <v/>
       </c>
-      <c r="W22" s="19">
+      <c r="W22" s="20">
         <f>MIN(V22,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,V22-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="X22" s="19">
+      <c r="X22" s="20">
         <f>U22*FERTILIZER_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="Y22" s="19">
+      <c r="Y22" s="20">
         <f>W22+X22</f>
         <v/>
       </c>
-      <c r="Z22" s="19">
+      <c r="Z22" s="20">
         <f>Y22-Y21</f>
         <v/>
       </c>
-      <c r="AA22" s="19">
+      <c r="AA22" s="20">
         <f>PRICE_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="AB22" s="22">
+      <c r="AB22" s="24">
         <f>IF(Z22&lt;=PRICE_PER_BED_MES,1,0)</f>
         <v/>
       </c>
-      <c r="AC22" s="22">
+      <c r="AC22" s="24">
         <f>AC21*AB22</f>
         <v/>
       </c>
@@ -3715,31 +3766,31 @@
         <f>A23*HRS_PER_BED_WEEK_TOM*WEEKS*(1+DIM_PCT_TOM)^A23</f>
         <v/>
       </c>
-      <c r="C23" s="19">
+      <c r="C23" s="20">
         <f>MIN(B23,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,B23-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="20">
         <f>A23*FERTILIZER_PER_BED_TOM</f>
         <v/>
       </c>
-      <c r="E23" s="19">
+      <c r="E23" s="20">
         <f>C23+D23</f>
         <v/>
       </c>
-      <c r="F23" s="19">
+      <c r="F23" s="20">
         <f>E23-E22</f>
         <v/>
       </c>
-      <c r="G23" s="19">
+      <c r="G23" s="20">
         <f>PRICE_PER_BED_TOM</f>
         <v/>
       </c>
-      <c r="H23" s="22">
+      <c r="H23" s="24">
         <f>IF(F23&lt;=PRICE_PER_BED_TOM,1,0)</f>
         <v/>
       </c>
-      <c r="I23" s="22">
+      <c r="I23" s="24">
         <f>I22*H23</f>
         <v/>
       </c>
@@ -3750,31 +3801,31 @@
         <f>K23*HRS_PER_BED_WEEK_CAR*WEEKS*(1+DIM_PCT_CAR)^K23</f>
         <v/>
       </c>
-      <c r="M23" s="19">
+      <c r="M23" s="20">
         <f>MIN(L23,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,L23-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="N23" s="19">
+      <c r="N23" s="20">
         <f>K23*FERTILIZER_PER_BED_CAR</f>
         <v/>
       </c>
-      <c r="O23" s="19">
+      <c r="O23" s="20">
         <f>M23+N23</f>
         <v/>
       </c>
-      <c r="P23" s="19">
+      <c r="P23" s="20">
         <f>O23-O22</f>
         <v/>
       </c>
-      <c r="Q23" s="19">
+      <c r="Q23" s="20">
         <f>PRICE_PER_BED_CAR</f>
         <v/>
       </c>
-      <c r="R23" s="22">
+      <c r="R23" s="24">
         <f>IF(P23&lt;=PRICE_PER_BED_CAR,1,0)</f>
         <v/>
       </c>
-      <c r="S23" s="22">
+      <c r="S23" s="24">
         <f>S22*R23</f>
         <v/>
       </c>
@@ -3785,31 +3836,31 @@
         <f>U23*HRS_PER_BED_WEEK_MES*WEEKS*(1+DIM_PCT_MES)^U23</f>
         <v/>
       </c>
-      <c r="W23" s="19">
+      <c r="W23" s="20">
         <f>MIN(V23,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,V23-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="X23" s="19">
+      <c r="X23" s="20">
         <f>U23*FERTILIZER_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="Y23" s="19">
+      <c r="Y23" s="20">
         <f>W23+X23</f>
         <v/>
       </c>
-      <c r="Z23" s="19">
+      <c r="Z23" s="20">
         <f>Y23-Y22</f>
         <v/>
       </c>
-      <c r="AA23" s="19">
+      <c r="AA23" s="20">
         <f>PRICE_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="AB23" s="22">
+      <c r="AB23" s="24">
         <f>IF(Z23&lt;=PRICE_PER_BED_MES,1,0)</f>
         <v/>
       </c>
-      <c r="AC23" s="22">
+      <c r="AC23" s="24">
         <f>AC22*AB23</f>
         <v/>
       </c>
@@ -3822,31 +3873,31 @@
         <f>A24*HRS_PER_BED_WEEK_TOM*WEEKS*(1+DIM_PCT_TOM)^A24</f>
         <v/>
       </c>
-      <c r="C24" s="19">
+      <c r="C24" s="20">
         <f>MIN(B24,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,B24-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="20">
         <f>A24*FERTILIZER_PER_BED_TOM</f>
         <v/>
       </c>
-      <c r="E24" s="19">
+      <c r="E24" s="20">
         <f>C24+D24</f>
         <v/>
       </c>
-      <c r="F24" s="19">
+      <c r="F24" s="20">
         <f>E24-E23</f>
         <v/>
       </c>
-      <c r="G24" s="19">
+      <c r="G24" s="20">
         <f>PRICE_PER_BED_TOM</f>
         <v/>
       </c>
-      <c r="H24" s="22">
+      <c r="H24" s="24">
         <f>IF(F24&lt;=PRICE_PER_BED_TOM,1,0)</f>
         <v/>
       </c>
-      <c r="I24" s="22">
+      <c r="I24" s="24">
         <f>I23*H24</f>
         <v/>
       </c>
@@ -3857,31 +3908,31 @@
         <f>K24*HRS_PER_BED_WEEK_CAR*WEEKS*(1+DIM_PCT_CAR)^K24</f>
         <v/>
       </c>
-      <c r="M24" s="19">
+      <c r="M24" s="20">
         <f>MIN(L24,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,L24-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="N24" s="19">
+      <c r="N24" s="20">
         <f>K24*FERTILIZER_PER_BED_CAR</f>
         <v/>
       </c>
-      <c r="O24" s="19">
+      <c r="O24" s="20">
         <f>M24+N24</f>
         <v/>
       </c>
-      <c r="P24" s="19">
+      <c r="P24" s="20">
         <f>O24-O23</f>
         <v/>
       </c>
-      <c r="Q24" s="19">
+      <c r="Q24" s="20">
         <f>PRICE_PER_BED_CAR</f>
         <v/>
       </c>
-      <c r="R24" s="22">
+      <c r="R24" s="24">
         <f>IF(P24&lt;=PRICE_PER_BED_CAR,1,0)</f>
         <v/>
       </c>
-      <c r="S24" s="22">
+      <c r="S24" s="24">
         <f>S23*R24</f>
         <v/>
       </c>
@@ -3892,31 +3943,31 @@
         <f>U24*HRS_PER_BED_WEEK_MES*WEEKS*(1+DIM_PCT_MES)^U24</f>
         <v/>
       </c>
-      <c r="W24" s="19">
+      <c r="W24" s="20">
         <f>MIN(V24,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,V24-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="X24" s="19">
+      <c r="X24" s="20">
         <f>U24*FERTILIZER_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="Y24" s="19">
+      <c r="Y24" s="20">
         <f>W24+X24</f>
         <v/>
       </c>
-      <c r="Z24" s="19">
+      <c r="Z24" s="20">
         <f>Y24-Y23</f>
         <v/>
       </c>
-      <c r="AA24" s="19">
+      <c r="AA24" s="20">
         <f>PRICE_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="AB24" s="22">
+      <c r="AB24" s="24">
         <f>IF(Z24&lt;=PRICE_PER_BED_MES,1,0)</f>
         <v/>
       </c>
-      <c r="AC24" s="22">
+      <c r="AC24" s="24">
         <f>AC23*AB24</f>
         <v/>
       </c>
@@ -3929,31 +3980,31 @@
         <f>A25*HRS_PER_BED_WEEK_TOM*WEEKS*(1+DIM_PCT_TOM)^A25</f>
         <v/>
       </c>
-      <c r="C25" s="19">
+      <c r="C25" s="20">
         <f>MIN(B25,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,B25-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="20">
         <f>A25*FERTILIZER_PER_BED_TOM</f>
         <v/>
       </c>
-      <c r="E25" s="19">
+      <c r="E25" s="20">
         <f>C25+D25</f>
         <v/>
       </c>
-      <c r="F25" s="19">
+      <c r="F25" s="20">
         <f>E25-E24</f>
         <v/>
       </c>
-      <c r="G25" s="19">
+      <c r="G25" s="20">
         <f>PRICE_PER_BED_TOM</f>
         <v/>
       </c>
-      <c r="H25" s="22">
+      <c r="H25" s="24">
         <f>IF(F25&lt;=PRICE_PER_BED_TOM,1,0)</f>
         <v/>
       </c>
-      <c r="I25" s="22">
+      <c r="I25" s="24">
         <f>I24*H25</f>
         <v/>
       </c>
@@ -3964,31 +4015,31 @@
         <f>K25*HRS_PER_BED_WEEK_CAR*WEEKS*(1+DIM_PCT_CAR)^K25</f>
         <v/>
       </c>
-      <c r="M25" s="19">
+      <c r="M25" s="20">
         <f>MIN(L25,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,L25-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="N25" s="19">
+      <c r="N25" s="20">
         <f>K25*FERTILIZER_PER_BED_CAR</f>
         <v/>
       </c>
-      <c r="O25" s="19">
+      <c r="O25" s="20">
         <f>M25+N25</f>
         <v/>
       </c>
-      <c r="P25" s="19">
+      <c r="P25" s="20">
         <f>O25-O24</f>
         <v/>
       </c>
-      <c r="Q25" s="19">
+      <c r="Q25" s="20">
         <f>PRICE_PER_BED_CAR</f>
         <v/>
       </c>
-      <c r="R25" s="22">
+      <c r="R25" s="24">
         <f>IF(P25&lt;=PRICE_PER_BED_CAR,1,0)</f>
         <v/>
       </c>
-      <c r="S25" s="22">
+      <c r="S25" s="24">
         <f>S24*R25</f>
         <v/>
       </c>
@@ -3999,31 +4050,31 @@
         <f>U25*HRS_PER_BED_WEEK_MES*WEEKS*(1+DIM_PCT_MES)^U25</f>
         <v/>
       </c>
-      <c r="W25" s="19">
+      <c r="W25" s="20">
         <f>MIN(V25,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,V25-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="X25" s="19">
+      <c r="X25" s="20">
         <f>U25*FERTILIZER_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="Y25" s="19">
+      <c r="Y25" s="20">
         <f>W25+X25</f>
         <v/>
       </c>
-      <c r="Z25" s="19">
+      <c r="Z25" s="20">
         <f>Y25-Y24</f>
         <v/>
       </c>
-      <c r="AA25" s="19">
+      <c r="AA25" s="20">
         <f>PRICE_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="AB25" s="22">
+      <c r="AB25" s="24">
         <f>IF(Z25&lt;=PRICE_PER_BED_MES,1,0)</f>
         <v/>
       </c>
-      <c r="AC25" s="22">
+      <c r="AC25" s="24">
         <f>AC24*AB25</f>
         <v/>
       </c>
@@ -4036,31 +4087,31 @@
         <f>A26*HRS_PER_BED_WEEK_TOM*WEEKS*(1+DIM_PCT_TOM)^A26</f>
         <v/>
       </c>
-      <c r="C26" s="19">
+      <c r="C26" s="20">
         <f>MIN(B26,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,B26-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="20">
         <f>A26*FERTILIZER_PER_BED_TOM</f>
         <v/>
       </c>
-      <c r="E26" s="19">
+      <c r="E26" s="20">
         <f>C26+D26</f>
         <v/>
       </c>
-      <c r="F26" s="19">
+      <c r="F26" s="20">
         <f>E26-E25</f>
         <v/>
       </c>
-      <c r="G26" s="19">
+      <c r="G26" s="20">
         <f>PRICE_PER_BED_TOM</f>
         <v/>
       </c>
-      <c r="H26" s="22">
+      <c r="H26" s="24">
         <f>IF(F26&lt;=PRICE_PER_BED_TOM,1,0)</f>
         <v/>
       </c>
-      <c r="I26" s="22">
+      <c r="I26" s="24">
         <f>I25*H26</f>
         <v/>
       </c>
@@ -4071,31 +4122,31 @@
         <f>K26*HRS_PER_BED_WEEK_CAR*WEEKS*(1+DIM_PCT_CAR)^K26</f>
         <v/>
       </c>
-      <c r="M26" s="19">
+      <c r="M26" s="20">
         <f>MIN(L26,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,L26-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="N26" s="19">
+      <c r="N26" s="20">
         <f>K26*FERTILIZER_PER_BED_CAR</f>
         <v/>
       </c>
-      <c r="O26" s="19">
+      <c r="O26" s="20">
         <f>M26+N26</f>
         <v/>
       </c>
-      <c r="P26" s="19">
+      <c r="P26" s="20">
         <f>O26-O25</f>
         <v/>
       </c>
-      <c r="Q26" s="19">
+      <c r="Q26" s="20">
         <f>PRICE_PER_BED_CAR</f>
         <v/>
       </c>
-      <c r="R26" s="22">
+      <c r="R26" s="24">
         <f>IF(P26&lt;=PRICE_PER_BED_CAR,1,0)</f>
         <v/>
       </c>
-      <c r="S26" s="22">
+      <c r="S26" s="24">
         <f>S25*R26</f>
         <v/>
       </c>
@@ -4106,31 +4157,31 @@
         <f>U26*HRS_PER_BED_WEEK_MES*WEEKS*(1+DIM_PCT_MES)^U26</f>
         <v/>
       </c>
-      <c r="W26" s="19">
+      <c r="W26" s="20">
         <f>MIN(V26,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,V26-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="X26" s="19">
+      <c r="X26" s="20">
         <f>U26*FERTILIZER_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="Y26" s="19">
+      <c r="Y26" s="20">
         <f>W26+X26</f>
         <v/>
       </c>
-      <c r="Z26" s="19">
+      <c r="Z26" s="20">
         <f>Y26-Y25</f>
         <v/>
       </c>
-      <c r="AA26" s="19">
+      <c r="AA26" s="20">
         <f>PRICE_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="AB26" s="22">
+      <c r="AB26" s="24">
         <f>IF(Z26&lt;=PRICE_PER_BED_MES,1,0)</f>
         <v/>
       </c>
-      <c r="AC26" s="22">
+      <c r="AC26" s="24">
         <f>AC25*AB26</f>
         <v/>
       </c>
@@ -4143,31 +4194,31 @@
         <f>A27*HRS_PER_BED_WEEK_TOM*WEEKS*(1+DIM_PCT_TOM)^A27</f>
         <v/>
       </c>
-      <c r="C27" s="19">
+      <c r="C27" s="20">
         <f>MIN(B27,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,B27-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="D27" s="19">
+      <c r="D27" s="20">
         <f>A27*FERTILIZER_PER_BED_TOM</f>
         <v/>
       </c>
-      <c r="E27" s="19">
+      <c r="E27" s="20">
         <f>C27+D27</f>
         <v/>
       </c>
-      <c r="F27" s="19">
+      <c r="F27" s="20">
         <f>E27-E26</f>
         <v/>
       </c>
-      <c r="G27" s="19">
+      <c r="G27" s="20">
         <f>PRICE_PER_BED_TOM</f>
         <v/>
       </c>
-      <c r="H27" s="22">
+      <c r="H27" s="24">
         <f>IF(F27&lt;=PRICE_PER_BED_TOM,1,0)</f>
         <v/>
       </c>
-      <c r="I27" s="22">
+      <c r="I27" s="24">
         <f>I26*H27</f>
         <v/>
       </c>
@@ -4178,31 +4229,31 @@
         <f>K27*HRS_PER_BED_WEEK_CAR*WEEKS*(1+DIM_PCT_CAR)^K27</f>
         <v/>
       </c>
-      <c r="M27" s="19">
+      <c r="M27" s="20">
         <f>MIN(L27,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,L27-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="N27" s="19">
+      <c r="N27" s="20">
         <f>K27*FERTILIZER_PER_BED_CAR</f>
         <v/>
       </c>
-      <c r="O27" s="19">
+      <c r="O27" s="20">
         <f>M27+N27</f>
         <v/>
       </c>
-      <c r="P27" s="19">
+      <c r="P27" s="20">
         <f>O27-O26</f>
         <v/>
       </c>
-      <c r="Q27" s="19">
+      <c r="Q27" s="20">
         <f>PRICE_PER_BED_CAR</f>
         <v/>
       </c>
-      <c r="R27" s="22">
+      <c r="R27" s="24">
         <f>IF(P27&lt;=PRICE_PER_BED_CAR,1,0)</f>
         <v/>
       </c>
-      <c r="S27" s="22">
+      <c r="S27" s="24">
         <f>S26*R27</f>
         <v/>
       </c>
@@ -4213,31 +4264,31 @@
         <f>U27*HRS_PER_BED_WEEK_MES*WEEKS*(1+DIM_PCT_MES)^U27</f>
         <v/>
       </c>
-      <c r="W27" s="19">
+      <c r="W27" s="20">
         <f>MIN(V27,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,V27-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="X27" s="19">
+      <c r="X27" s="20">
         <f>U27*FERTILIZER_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="Y27" s="19">
+      <c r="Y27" s="20">
         <f>W27+X27</f>
         <v/>
       </c>
-      <c r="Z27" s="19">
+      <c r="Z27" s="20">
         <f>Y27-Y26</f>
         <v/>
       </c>
-      <c r="AA27" s="19">
+      <c r="AA27" s="20">
         <f>PRICE_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="AB27" s="22">
+      <c r="AB27" s="24">
         <f>IF(Z27&lt;=PRICE_PER_BED_MES,1,0)</f>
         <v/>
       </c>
-      <c r="AC27" s="22">
+      <c r="AC27" s="24">
         <f>AC26*AB27</f>
         <v/>
       </c>
@@ -4250,31 +4301,31 @@
         <f>U28*HRS_PER_BED_WEEK_MES*WEEKS*(1+DIM_PCT_MES)^U28</f>
         <v/>
       </c>
-      <c r="W28" s="19">
+      <c r="W28" s="20">
         <f>MIN(V28,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,V28-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="X28" s="19">
+      <c r="X28" s="20">
         <f>U28*FERTILIZER_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="Y28" s="19">
+      <c r="Y28" s="20">
         <f>W28+X28</f>
         <v/>
       </c>
-      <c r="Z28" s="19">
+      <c r="Z28" s="20">
         <f>Y28-Y27</f>
         <v/>
       </c>
-      <c r="AA28" s="19">
+      <c r="AA28" s="20">
         <f>PRICE_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="AB28" s="22">
+      <c r="AB28" s="24">
         <f>IF(Z28&lt;=PRICE_PER_BED_MES,1,0)</f>
         <v/>
       </c>
-      <c r="AC28" s="22">
+      <c r="AC28" s="24">
         <f>AC27*AB28</f>
         <v/>
       </c>
@@ -4285,7 +4336,7 @@
           <t>Standalone P = MC point</t>
         </is>
       </c>
-      <c r="F29" s="23">
+      <c r="F29" s="25">
         <f>SUM(I8:I27)</f>
         <v/>
       </c>
@@ -4294,7 +4345,7 @@
           <t>Standalone P = MC point</t>
         </is>
       </c>
-      <c r="P29" s="23">
+      <c r="P29" s="25">
         <f>SUM(S8:S27)</f>
         <v/>
       </c>
@@ -4305,31 +4356,31 @@
         <f>U29*HRS_PER_BED_WEEK_MES*WEEKS*(1+DIM_PCT_MES)^U29</f>
         <v/>
       </c>
-      <c r="W29" s="19">
+      <c r="W29" s="20">
         <f>MIN(V29,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,V29-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="X29" s="19">
+      <c r="X29" s="20">
         <f>U29*FERTILIZER_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="Y29" s="19">
+      <c r="Y29" s="20">
         <f>W29+X29</f>
         <v/>
       </c>
-      <c r="Z29" s="19">
+      <c r="Z29" s="20">
         <f>Y29-Y28</f>
         <v/>
       </c>
-      <c r="AA29" s="19">
+      <c r="AA29" s="20">
         <f>PRICE_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="AB29" s="22">
+      <c r="AB29" s="24">
         <f>IF(Z29&lt;=PRICE_PER_BED_MES,1,0)</f>
         <v/>
       </c>
-      <c r="AC29" s="22">
+      <c r="AC29" s="24">
         <f>AC28*AB29</f>
         <v/>
       </c>
@@ -4352,31 +4403,31 @@
         <f>U30*HRS_PER_BED_WEEK_MES*WEEKS*(1+DIM_PCT_MES)^U30</f>
         <v/>
       </c>
-      <c r="W30" s="19">
+      <c r="W30" s="20">
         <f>MIN(V30,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,V30-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="X30" s="19">
+      <c r="X30" s="20">
         <f>U30*FERTILIZER_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="Y30" s="19">
+      <c r="Y30" s="20">
         <f>W30+X30</f>
         <v/>
       </c>
-      <c r="Z30" s="19">
+      <c r="Z30" s="20">
         <f>Y30-Y29</f>
         <v/>
       </c>
-      <c r="AA30" s="19">
+      <c r="AA30" s="20">
         <f>PRICE_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="AB30" s="22">
+      <c r="AB30" s="24">
         <f>IF(Z30&lt;=PRICE_PER_BED_MES,1,0)</f>
         <v/>
       </c>
-      <c r="AC30" s="22">
+      <c r="AC30" s="24">
         <f>AC29*AB30</f>
         <v/>
       </c>
@@ -4399,31 +4450,31 @@
         <f>U31*HRS_PER_BED_WEEK_MES*WEEKS*(1+DIM_PCT_MES)^U31</f>
         <v/>
       </c>
-      <c r="W31" s="19">
+      <c r="W31" s="20">
         <f>MIN(V31,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,V31-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="X31" s="19">
+      <c r="X31" s="20">
         <f>U31*FERTILIZER_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="Y31" s="19">
+      <c r="Y31" s="20">
         <f>W31+X31</f>
         <v/>
       </c>
-      <c r="Z31" s="19">
+      <c r="Z31" s="20">
         <f>Y31-Y30</f>
         <v/>
       </c>
-      <c r="AA31" s="19">
+      <c r="AA31" s="20">
         <f>PRICE_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="AB31" s="22">
+      <c r="AB31" s="24">
         <f>IF(Z31&lt;=PRICE_PER_BED_MES,1,0)</f>
         <v/>
       </c>
-      <c r="AC31" s="22">
+      <c r="AC31" s="24">
         <f>AC30*AB31</f>
         <v/>
       </c>
@@ -4436,31 +4487,31 @@
         <f>U32*HRS_PER_BED_WEEK_MES*WEEKS*(1+DIM_PCT_MES)^U32</f>
         <v/>
       </c>
-      <c r="W32" s="19">
+      <c r="W32" s="20">
         <f>MIN(V32,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,V32-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="X32" s="19">
+      <c r="X32" s="20">
         <f>U32*FERTILIZER_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="Y32" s="19">
+      <c r="Y32" s="20">
         <f>W32+X32</f>
         <v/>
       </c>
-      <c r="Z32" s="19">
+      <c r="Z32" s="20">
         <f>Y32-Y31</f>
         <v/>
       </c>
-      <c r="AA32" s="19">
+      <c r="AA32" s="20">
         <f>PRICE_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="AB32" s="22">
+      <c r="AB32" s="24">
         <f>IF(Z32&lt;=PRICE_PER_BED_MES,1,0)</f>
         <v/>
       </c>
-      <c r="AC32" s="22">
+      <c r="AC32" s="24">
         <f>AC31*AB32</f>
         <v/>
       </c>
@@ -4473,31 +4524,31 @@
         <f>U33*HRS_PER_BED_WEEK_MES*WEEKS*(1+DIM_PCT_MES)^U33</f>
         <v/>
       </c>
-      <c r="W33" s="19">
+      <c r="W33" s="20">
         <f>MIN(V33,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,V33-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="X33" s="19">
+      <c r="X33" s="20">
         <f>U33*FERTILIZER_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="Y33" s="19">
+      <c r="Y33" s="20">
         <f>W33+X33</f>
         <v/>
       </c>
-      <c r="Z33" s="19">
+      <c r="Z33" s="20">
         <f>Y33-Y32</f>
         <v/>
       </c>
-      <c r="AA33" s="19">
+      <c r="AA33" s="20">
         <f>PRICE_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="AB33" s="22">
+      <c r="AB33" s="24">
         <f>IF(Z33&lt;=PRICE_PER_BED_MES,1,0)</f>
         <v/>
       </c>
-      <c r="AC33" s="22">
+      <c r="AC33" s="24">
         <f>AC32*AB33</f>
         <v/>
       </c>
@@ -4510,31 +4561,31 @@
         <f>U34*HRS_PER_BED_WEEK_MES*WEEKS*(1+DIM_PCT_MES)^U34</f>
         <v/>
       </c>
-      <c r="W34" s="19">
+      <c r="W34" s="20">
         <f>MIN(V34,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,V34-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="X34" s="19">
+      <c r="X34" s="20">
         <f>U34*FERTILIZER_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="Y34" s="19">
+      <c r="Y34" s="20">
         <f>W34+X34</f>
         <v/>
       </c>
-      <c r="Z34" s="19">
+      <c r="Z34" s="20">
         <f>Y34-Y33</f>
         <v/>
       </c>
-      <c r="AA34" s="19">
+      <c r="AA34" s="20">
         <f>PRICE_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="AB34" s="22">
+      <c r="AB34" s="24">
         <f>IF(Z34&lt;=PRICE_PER_BED_MES,1,0)</f>
         <v/>
       </c>
-      <c r="AC34" s="22">
+      <c r="AC34" s="24">
         <f>AC33*AB34</f>
         <v/>
       </c>
@@ -4547,31 +4598,31 @@
         <f>U35*HRS_PER_BED_WEEK_MES*WEEKS*(1+DIM_PCT_MES)^U35</f>
         <v/>
       </c>
-      <c r="W35" s="19">
+      <c r="W35" s="20">
         <f>MIN(V35,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,V35-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="X35" s="19">
+      <c r="X35" s="20">
         <f>U35*FERTILIZER_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="Y35" s="19">
+      <c r="Y35" s="20">
         <f>W35+X35</f>
         <v/>
       </c>
-      <c r="Z35" s="19">
+      <c r="Z35" s="20">
         <f>Y35-Y34</f>
         <v/>
       </c>
-      <c r="AA35" s="19">
+      <c r="AA35" s="20">
         <f>PRICE_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="AB35" s="22">
+      <c r="AB35" s="24">
         <f>IF(Z35&lt;=PRICE_PER_BED_MES,1,0)</f>
         <v/>
       </c>
-      <c r="AC35" s="22">
+      <c r="AC35" s="24">
         <f>AC34*AB35</f>
         <v/>
       </c>
@@ -4584,31 +4635,31 @@
         <f>U36*HRS_PER_BED_WEEK_MES*WEEKS*(1+DIM_PCT_MES)^U36</f>
         <v/>
       </c>
-      <c r="W36" s="19">
+      <c r="W36" s="20">
         <f>MIN(V36,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,V36-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="X36" s="19">
+      <c r="X36" s="20">
         <f>U36*FERTILIZER_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="Y36" s="19">
+      <c r="Y36" s="20">
         <f>W36+X36</f>
         <v/>
       </c>
-      <c r="Z36" s="19">
+      <c r="Z36" s="20">
         <f>Y36-Y35</f>
         <v/>
       </c>
-      <c r="AA36" s="19">
+      <c r="AA36" s="20">
         <f>PRICE_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="AB36" s="22">
+      <c r="AB36" s="24">
         <f>IF(Z36&lt;=PRICE_PER_BED_MES,1,0)</f>
         <v/>
       </c>
-      <c r="AC36" s="22">
+      <c r="AC36" s="24">
         <f>AC35*AB36</f>
         <v/>
       </c>
@@ -4621,31 +4672,31 @@
         <f>U37*HRS_PER_BED_WEEK_MES*WEEKS*(1+DIM_PCT_MES)^U37</f>
         <v/>
       </c>
-      <c r="W37" s="19">
+      <c r="W37" s="20">
         <f>MIN(V37,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,V37-FARMER_FIELD_HRS)*TEMP_RATE</f>
         <v/>
       </c>
-      <c r="X37" s="19">
+      <c r="X37" s="20">
         <f>U37*FERTILIZER_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="Y37" s="19">
+      <c r="Y37" s="20">
         <f>W37+X37</f>
         <v/>
       </c>
-      <c r="Z37" s="19">
+      <c r="Z37" s="20">
         <f>Y37-Y36</f>
         <v/>
       </c>
-      <c r="AA37" s="19">
+      <c r="AA37" s="20">
         <f>PRICE_PER_BED_MES</f>
         <v/>
       </c>
-      <c r="AB37" s="22">
+      <c r="AB37" s="24">
         <f>IF(Z37&lt;=PRICE_PER_BED_MES,1,0)</f>
         <v/>
       </c>
-      <c r="AC37" s="22">
+      <c r="AC37" s="24">
         <f>AC36*AB37</f>
         <v/>
       </c>
@@ -4656,7 +4707,7 @@
           <t>Standalone P = MC point</t>
         </is>
       </c>
-      <c r="Z39" s="23">
+      <c r="Z39" s="25">
         <f>SUM(AC8:AC37)</f>
         <v/>
       </c>
@@ -4747,11 +4798,11 @@
         <f>10</f>
         <v/>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="15">
         <f>BEDS_TOMATO</f>
         <v/>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="19">
         <f>IF(C5=B5,"PASS","FAIL")</f>
         <v/>
       </c>
@@ -4771,11 +4822,11 @@
         <f>20</f>
         <v/>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="15">
         <f>BEDS_CARROT</f>
         <v/>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="19">
         <f>IF(C6=B6,"PASS","FAIL")</f>
         <v/>
       </c>
@@ -4795,11 +4846,11 @@
         <f>30</f>
         <v/>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="15">
         <f>BEDS_MESCLUN</f>
         <v/>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="19">
         <f>IF(C7=B7,"PASS","FAIL")</f>
         <v/>
       </c>
@@ -4819,11 +4870,11 @@
         <f>60</f>
         <v/>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="15">
         <f>BEDS_TOMATO+BEDS_CARROT+BEDS_MESCLUN</f>
         <v/>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="19">
         <f>IF(C8=B8,"PASS","FAIL")</f>
         <v/>
       </c>
@@ -4839,15 +4890,15 @@
           <t>Season profit</t>
         </is>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="20">
         <f>42762</f>
         <v/>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="21">
         <f>SEASON_PROFIT</f>
         <v/>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="19">
         <f>IF(ABS(C9-B9)&lt;=5,"PASS","FAIL")</f>
         <v/>
       </c>
@@ -4867,11 +4918,11 @@
         <f>10</f>
         <v/>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="15">
         <f>PMC_TOM</f>
         <v/>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="19">
         <f>IF(ABS(C10-B10)&lt;=1,"PASS","FAIL")</f>
         <v/>
       </c>
@@ -4891,11 +4942,11 @@
         <f>10</f>
         <v/>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="15">
         <f>PMC_CAR</f>
         <v/>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="19">
         <f>IF(ABS(C11-B11)&lt;=1,"PASS","FAIL")</f>
         <v/>
       </c>
@@ -4915,11 +4966,11 @@
         <f>6</f>
         <v/>
       </c>
-      <c r="C12" s="24">
+      <c r="C12" s="15">
         <f>PMC_MES</f>
         <v/>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="19">
         <f>IF(ABS(C12-B12)&lt;=1,"PASS","FAIL")</f>
         <v/>
       </c>
@@ -4939,11 +4990,11 @@
         <f>99</f>
         <v/>
       </c>
-      <c r="C13" s="18">
+      <c r="C13" s="17">
         <f>HAND_CHECK_Q1</f>
         <v/>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="19">
         <f>IF(ABS(C13-B13)&lt;=0.01,"PASS","FAIL")</f>
         <v/>
       </c>
@@ -4959,15 +5010,15 @@
           <t>Blended-rate allocation equals total labor cost</t>
         </is>
       </c>
-      <c r="B14" s="19">
+      <c r="B14" s="20">
         <f>'Cost structure'!B18</f>
         <v/>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="21">
         <f>'Cost structure'!B26</f>
         <v/>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="19">
         <f>IF(ABS(C14-B14)&lt;=0.01,"PASS","FAIL")</f>
         <v/>
       </c>
@@ -4987,11 +5038,11 @@
         <f>MAX_TEMPS</f>
         <v/>
       </c>
-      <c r="C15" s="24">
+      <c r="C15" s="15">
         <f>TEMPS_REQUIRED</f>
         <v/>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="19">
         <f>IF(C15&lt;=B15,"PASS","FAIL")</f>
         <v/>
       </c>
@@ -5011,11 +5062,11 @@
         <f>"PASS"</f>
         <v/>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="26">
         <f>CONSTRAINTS_ALL</f>
         <v/>
       </c>
-      <c r="D16" s="17">
+      <c r="D16" s="19">
         <f>IF(C16=B16,"PASS","FAIL")</f>
         <v/>
       </c>
@@ -5100,10 +5151,10 @@
           <t>0 / 0 / 0</t>
         </is>
       </c>
-      <c r="B26" s="26" t="n"/>
-      <c r="C26" s="26" t="n"/>
-      <c r="D26" s="26" t="n"/>
-      <c r="E26" s="26" t="n"/>
+      <c r="B26" s="27" t="n"/>
+      <c r="C26" s="27" t="n"/>
+      <c r="D26" s="27" t="n"/>
+      <c r="E26" s="27" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
@@ -5111,10 +5162,10 @@
           <t>20 / 0 / 0</t>
         </is>
       </c>
-      <c r="B27" s="26" t="n"/>
-      <c r="C27" s="26" t="n"/>
-      <c r="D27" s="26" t="n"/>
-      <c r="E27" s="26" t="n"/>
+      <c r="B27" s="27" t="n"/>
+      <c r="C27" s="27" t="n"/>
+      <c r="D27" s="27" t="n"/>
+      <c r="E27" s="27" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">

--- a/capabilities/marginal-analysis/model.xlsx
+++ b/capabilities/marginal-analysis/model.xlsx
@@ -60,42 +60,6 @@
     <definedName name="PMC_TOM">'MC schedules'!$F$29</definedName>
     <definedName name="PMC_CAR">'MC schedules'!$P$29</definedName>
     <definedName name="PMC_MES">'MC schedules'!$Z$39</definedName>
-    <definedName name="solver_opt" localSheetId="1" hidden="1">Optimization!$B$16</definedName>
-    <definedName name="solver_typ" localSheetId="1" hidden="1">1</definedName>
-    <definedName name="solver_val" localSheetId="1" hidden="1">0</definedName>
-    <definedName name="solver_adj" localSheetId="1" hidden="1">Optimization!$B$5:$B$7</definedName>
-    <definedName name="solver_eng" localSheetId="1" hidden="1">1</definedName>
-    <definedName name="solver_neg" localSheetId="1" hidden="1">1</definedName>
-    <definedName name="solver_num" localSheetId="1" hidden="1">4</definedName>
-    <definedName name="solver_lhs1" localSheetId="1" hidden="1">Optimization!$B$5:$B$7</definedName>
-    <definedName name="solver_rel1" localSheetId="1" hidden="1">4</definedName>
-    <definedName name="solver_rhs1" localSheetId="1" hidden="1">integer</definedName>
-    <definedName name="solver_lhs2" localSheetId="1" hidden="1">Optimization!$B$5:$B$7</definedName>
-    <definedName name="solver_rel2" localSheetId="1" hidden="1">1</definedName>
-    <definedName name="solver_rhs2" localSheetId="1" hidden="1">Optimization!$C$5:$C$7</definedName>
-    <definedName name="solver_lhs3" localSheetId="1" hidden="1">Optimization!$B$10</definedName>
-    <definedName name="solver_rel3" localSheetId="1" hidden="1">1</definedName>
-    <definedName name="solver_rhs3" localSheetId="1" hidden="1">Optimization!$C$10</definedName>
-    <definedName name="solver_lhs4" localSheetId="1" hidden="1">Optimization!$B$11</definedName>
-    <definedName name="solver_rel4" localSheetId="1" hidden="1">1</definedName>
-    <definedName name="solver_rhs4" localSheetId="1" hidden="1">Optimization!$C$11</definedName>
-    <definedName name="solver_pre" localSheetId="1" hidden="1">0.000001</definedName>
-    <definedName name="solver_tol" localSheetId="1" hidden="1">0.01</definedName>
-    <definedName name="solver_itr" localSheetId="1" hidden="1">2147483647</definedName>
-    <definedName name="solver_ver" localSheetId="1" hidden="1">3</definedName>
-    <definedName name="solver_drv" localSheetId="1" hidden="1">1</definedName>
-    <definedName name="solver_est" localSheetId="1" hidden="1">1</definedName>
-    <definedName name="solver_sho" localSheetId="1" hidden="1">2</definedName>
-    <definedName name="solver_scl" localSheetId="1" hidden="1">2</definedName>
-    <definedName name="solver_rlx" localSheetId="1" hidden="1">2</definedName>
-    <definedName name="solver_ssz" localSheetId="1" hidden="1">2</definedName>
-    <definedName name="solver_mni" localSheetId="1" hidden="1">30</definedName>
-    <definedName name="solver_mrt" localSheetId="1" hidden="1">0.075</definedName>
-    <definedName name="solver_nod" localSheetId="1" hidden="1">2147483647</definedName>
-    <definedName name="solver_rsd" localSheetId="1" hidden="1">0</definedName>
-    <definedName name="solver_pop" localSheetId="1" hidden="1">100</definedName>
-    <definedName name="solver_rbv" localSheetId="1" hidden="1">1</definedName>
-    <definedName name="solver_time" localSheetId="1" hidden="1">2147483647</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1082,7 +1046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1102,7 +1066,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>The Solver model is already saved in this workbook. Open Data &gt; Solver and it loads configured — just press Solve.</t>
+          <t>Enter the Solver settings below by hand — Data &gt; Solver. Five constraints, about two minutes.</t>
         </is>
       </c>
     </row>
@@ -1122,8 +1086,6 @@
           <t>Cap</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
@@ -1458,6 +1420,193 @@
       <c r="A34" s="2" t="inlineStr">
         <is>
           <t>tick Solver Add-in.  On Mac: Tools &gt; Excel Add-ins &gt; tick Solver.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Solver settings — type these into Data &gt; Solver</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t>Set Objective</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>$B$16</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>To</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>By Changing Variable Cells</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>$B$5:$B$7</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="inlineStr"/>
+      <c r="B40" s="13" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Subject to the Constraints — click Add for each</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Cell Reference</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Relation</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Constraint</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="13" t="inlineStr">
+        <is>
+          <t>$B$5:$B$7</t>
+        </is>
+      </c>
+      <c r="B43" s="13" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C43" s="13" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="inlineStr">
+        <is>
+          <t>$B$5:$B$7</t>
+        </is>
+      </c>
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="C44" s="13" t="inlineStr">
+        <is>
+          <t>$C$5:$C$7</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="13" t="inlineStr">
+        <is>
+          <t>$B$10</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="C45" s="13" t="inlineStr">
+        <is>
+          <t>$C$10</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="13" t="inlineStr">
+        <is>
+          <t>$B$11</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="C46" s="13" t="inlineStr">
+        <is>
+          <t>$C$11</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Select a Solving Method: GRG Nonlinear.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Tick "Make Unconstrained Variables Non-Negative".</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>For the "int" constraint: pick $B$5:$B$7, then choose "int" from the relation dropdown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>The Constraint box fills in "integer" by itself — do not type it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>If Solver is not on the Data ribbon: File &gt; Options &gt; Add-ins &gt; Manage: Excel Add-ins &gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Go &gt; tick Solver Add-in.  Mac: Tools &gt; Excel Add-ins &gt; tick Solver.</t>
         </is>
       </c>
     </row>

--- a/capabilities/marginal-analysis/model.xlsx
+++ b/capabilities/marginal-analysis/model.xlsx
@@ -9,8 +9,8 @@
   <sheets>
     <sheet name="Inputs" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Optimization" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Cost structure" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="MC schedules" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="CostStructure" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="MCSchedules" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Checks" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
@@ -44,22 +44,22 @@
     <definedName name="BEDS_CARROT">'Optimization'!$B$6</definedName>
     <definedName name="BEDS_MESCLUN">'Optimization'!$B$7</definedName>
     <definedName name="CONSTRAINTS_ALL">'Optimization'!$D$25</definedName>
-    <definedName name="TOTAL_LABOR_HRS">'Cost structure'!$B$8</definedName>
-    <definedName name="FARMER_HRS_USED">'Cost structure'!$B$11</definedName>
-    <definedName name="TEMP_HRS_USED">'Cost structure'!$B$12</definedName>
-    <definedName name="TEMPS_REQUIRED">'Cost structure'!$B$13</definedName>
-    <definedName name="FARMER_LABOR_COST">'Cost structure'!$B$16</definedName>
-    <definedName name="TEMP_LABOR_COST">'Cost structure'!$B$17</definedName>
-    <definedName name="TOTAL_LABOR_COST">'Cost structure'!$B$18</definedName>
-    <definedName name="BLENDED_RATE">'Cost structure'!$B$19</definedName>
-    <definedName name="SEASON_REVENUE">'Cost structure'!$B$29</definedName>
-    <definedName name="FERTILIZER_COST">'Cost structure'!$B$30</definedName>
-    <definedName name="TOTAL_COST_SEASON">'Cost structure'!$B$32</definedName>
-    <definedName name="SEASON_PROFIT">'Cost structure'!$B$34</definedName>
-    <definedName name="HAND_CHECK_Q1">'Cost structure'!$B$37</definedName>
-    <definedName name="PMC_TOM">'MC schedules'!$F$29</definedName>
-    <definedName name="PMC_CAR">'MC schedules'!$P$29</definedName>
-    <definedName name="PMC_MES">'MC schedules'!$Z$39</definedName>
+    <definedName name="TOTAL_LABOR_HRS">CostStructure!$B$8</definedName>
+    <definedName name="FARMER_HRS_USED">CostStructure!$B$11</definedName>
+    <definedName name="TEMP_HRS_USED">CostStructure!$B$12</definedName>
+    <definedName name="TEMPS_REQUIRED">CostStructure!$B$13</definedName>
+    <definedName name="FARMER_LABOR_COST">CostStructure!$B$16</definedName>
+    <definedName name="TEMP_LABOR_COST">CostStructure!$B$17</definedName>
+    <definedName name="TOTAL_LABOR_COST">CostStructure!$B$18</definedName>
+    <definedName name="BLENDED_RATE">CostStructure!$B$19</definedName>
+    <definedName name="SEASON_REVENUE">CostStructure!$B$29</definedName>
+    <definedName name="FERTILIZER_COST">CostStructure!$B$30</definedName>
+    <definedName name="TOTAL_COST_SEASON">CostStructure!$B$32</definedName>
+    <definedName name="SEASON_PROFIT">CostStructure!$B$34</definedName>
+    <definedName name="HAND_CHECK_Q1">CostStructure!$B$37</definedName>
+    <definedName name="PMC_TOM">MCSchedules!$F$29</definedName>
+    <definedName name="PMC_CAR">MCSchedules!$P$29</definedName>
+    <definedName name="PMC_MES">MCSchedules!$Z$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -584,6 +584,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -753,6 +754,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
@@ -1007,6 +1009,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
@@ -1070,6 +1073,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1144,6 +1148,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
@@ -1218,6 +1223,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
@@ -1236,6 +1242,7 @@
         <v/>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
@@ -1371,6 +1378,7 @@
         <v/>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
@@ -1423,6 +1431,7 @@
         </is>
       </c>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
@@ -1562,6 +1571,7 @@
         </is>
       </c>
     </row>
+    <row r="47"/>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
@@ -1645,6 +1655,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1706,6 +1717,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
@@ -1761,6 +1773,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
@@ -1827,6 +1840,7 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
@@ -1890,6 +1904,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
@@ -1975,6 +1990,7 @@
         </is>
       </c>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
@@ -2062,6 +2078,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -4850,6 +4867,7 @@
         <v/>
       </c>
     </row>
+    <row r="38"/>
     <row r="39">
       <c r="U39" s="3" t="inlineStr">
         <is>
@@ -4910,6 +4928,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -5160,11 +5179,11 @@
         </is>
       </c>
       <c r="B14" s="20">
-        <f>'Cost structure'!B18</f>
+        <f>CostStructure!B18</f>
         <v/>
       </c>
       <c r="C14" s="21">
-        <f>'Cost structure'!B26</f>
+        <f>CostStructure!B26</f>
         <v/>
       </c>
       <c r="D14" s="19">
@@ -5225,6 +5244,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
@@ -5260,6 +5280,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
@@ -5316,6 +5337,7 @@
       <c r="D27" s="27" t="n"/>
       <c r="E27" s="27" t="n"/>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>

--- a/capabilities/marginal-analysis/model.xlsx
+++ b/capabilities/marginal-analysis/model.xlsx
@@ -104,12 +104,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="#,##0.0;\(#,##0.0\);\-"/>
     <numFmt numFmtId="165" formatCode="\$#,##0;\(\$#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.000%"/>
     <numFmt numFmtId="167" formatCode="\$#,##0.00;\(\$#,##0.00\);\-"/>
     <numFmt numFmtId="168" formatCode="$#,##0;($#,##0);-"/>
+    <numFmt numFmtId="169" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -189,7 +190,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -212,11 +213,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -252,6 +267,14 @@
     <xf numFmtId="3" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="8" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4930,7 +4953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -5268,152 +5291,194 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>Hand check — LABOR_HRS(10) tomatoes</t>
+        </is>
+      </c>
+      <c r="B17" s="32">
+        <f>2334.368214</f>
+        <v/>
+      </c>
+      <c r="C17" s="33">
+        <f>'MCSchedules'!B17</f>
+        <v/>
+      </c>
+      <c r="D17" s="34">
+        <f>IF(ABS(C17-B17)&lt;=0.001,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="E17" s="30" t="inlineStr">
+        <is>
+          <t>Second anchor. A flat (1+DIM_PCT) instead of compounding returns 990 here but still 99 at q=1.</t>
+        </is>
+      </c>
+    </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>Farm Profit Lab — MC of the 7th tomato bed</t>
+        </is>
+      </c>
+      <c r="B18" s="35">
+        <f>5586</f>
+        <v/>
+      </c>
+      <c r="C18" s="36">
+        <f>'MCSchedules'!F14</f>
+        <v/>
+      </c>
+      <c r="D18" s="34">
+        <f>IF(ABS(C18-B18)&lt;=1,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="E18" s="30" t="inlineStr">
+        <is>
+          <t>Lab totals run $20,000 higher (fixed costs it includes); compare marginal, not total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Structural rules — verified by inspection, not by formula</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>- No error cells anywhere in the workbook — no #REF!, #DIV/0!, #NAME?, #VALUE! or #N/A.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>- Every calculated cell contains a formula referencing named ranges. No pasted values.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>- Every input is a real named range carrying the unit stated on the Inputs sheet.</t>
+          <t>- No error cells anywhere in the workbook — no #REF!, #DIV/0!, #NAME?, #VALUE! or #N/A.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>- Every calculated cell contains a formula referencing named ranges. No pasted values.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>- Every input is a real named range carrying the unit stated on the Inputs sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
           <t>- Spot-check: click any cell on Cost structure or MC schedules and confirm the formula bar shows a formula.</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Solver path-dependence — record both runs here during the audit</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>Starting point</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Tomatoes</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>Carrots</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>Mesclun</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>Season profit</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>0 / 0 / 0</t>
         </is>
       </c>
-      <c r="B26" s="28" t="n">
+      <c r="B28" s="28" t="n">
         <v>10</v>
       </c>
-      <c r="C26" s="28" t="n">
+      <c r="C28" s="28" t="n">
         <v>20</v>
       </c>
-      <c r="D26" s="28" t="n">
+      <c r="D28" s="28" t="n">
         <v>30</v>
       </c>
-      <c r="E26" s="29">
+      <c r="E28" s="29">
         <f>SEASON_PROFIT</f>
         <v/>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>20 / 0 / 0</t>
         </is>
       </c>
-      <c r="B27" s="28" t="n">
+      <c r="B29" s="28" t="n">
         <v>10</v>
       </c>
-      <c r="C27" s="28" t="n">
+      <c r="C29" s="28" t="n">
         <v>20</v>
       </c>
-      <c r="D27" s="28" t="n">
+      <c r="D29" s="28" t="n">
         <v>30</v>
       </c>
-      <c r="E27" s="29">
+      <c r="E29" s="29">
         <f>SEASON_PROFIT</f>
         <v/>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="30" t="inlineStr">
-        <is>
-          <t>Both starting points converged on the same answer: 10 / 20 / 30, season profit $42,762.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="30" t="inlineStr">
-        <is>
-          <t>No path dependence observed. Agreement across two starts is evidence the optimum is global,</t>
-        </is>
-      </c>
-    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="30" t="inlineStr">
         <is>
-          <t>not the first summit GRG Nonlinear happened to reach. Solver settings were identical in both runs;</t>
+          <t>Both starting points converged on the same answer: 10 / 20 / 30, season profit $42,762.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="30" t="inlineStr">
         <is>
+          <t>No path dependence observed. Agreement across two starts is evidence the optimum is global,</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="30" t="inlineStr">
+        <is>
+          <t>not the first summit GRG Nonlinear happened to reach. Solver settings were identical in both runs;</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="30" t="inlineStr">
+        <is>
           <t>only the contents of B5:B7 differed.</t>
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/capabilities/marginal-analysis/model.xlsx
+++ b/capabilities/marginal-analysis/model.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/seanbarnes/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/seanbarnes/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_5DBE778AA13D8A87141BB33C6089111AA8323812" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61709E9A-6F66-674D-A0B4-90B1D7E7D945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17080" yWindow="680" windowWidth="17120" windowHeight="19580" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6660" yWindow="680" windowWidth="25800" windowHeight="19580" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs" sheetId="1" r:id="rId1"/>
@@ -55,6 +55,8 @@
     <definedName name="PRICE_PER_BED_TOM">Inputs!$B$7</definedName>
     <definedName name="SEASON_PROFIT">CostStructure!$B$34</definedName>
     <definedName name="SEASON_REVENUE">CostStructure!$B$29</definedName>
+    <definedName name="SHADOW_CAR">Optimization!$J$61</definedName>
+    <definedName name="SHADOW_MES">Optimization!$J$62</definedName>
     <definedName name="solver_adj" localSheetId="1" hidden="1">Optimization!$B$5:$B$7</definedName>
     <definedName name="solver_cvg" localSheetId="1" hidden="1">0.0001</definedName>
     <definedName name="solver_drv" localSheetId="1" hidden="1">1</definedName>
@@ -123,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="231">
   <si>
     <t>Optimization</t>
   </si>
@@ -762,6 +764,60 @@
   </si>
   <si>
     <t>only the contents of B5:B7 differed.</t>
+  </si>
+  <si>
+    <t>Tom</t>
+  </si>
+  <si>
+    <t>Car</t>
+  </si>
+  <si>
+    <t>Mes</t>
+  </si>
+  <si>
+    <t>Labor hrs</t>
+  </si>
+  <si>
+    <t>Revenue</t>
+  </si>
+  <si>
+    <t>Profit</t>
+  </si>
+  <si>
+    <t>Shadow price</t>
+  </si>
+  <si>
+    <t>Total beds</t>
+  </si>
+  <si>
+    <t>Crop relaxed</t>
+  </si>
+  <si>
+    <t>Temp hrs</t>
+  </si>
+  <si>
+    <t>Feasible</t>
+  </si>
+  <si>
+    <t>Shadow prices of the binding bed caps — 3.13</t>
+  </si>
+  <si>
+    <t>Shadow price — carrot bed cap</t>
+  </si>
+  <si>
+    <t>Shadow price — mesclun bed cap</t>
+  </si>
+  <si>
+    <t>Shadow price equals PRICE - MC(cap+1) — carrots</t>
+  </si>
+  <si>
+    <t>Shadow price equals PRICE - MC(cap+1) — mesclun</t>
+  </si>
+  <si>
+    <t>Passes within +/- $5</t>
+  </si>
+  <si>
+    <t>Two routes through the model, no shared formula</t>
   </si>
 </sst>
 </file>
@@ -862,7 +918,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -900,11 +956,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -947,6 +1014,12 @@
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf applyFont="1" numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1598,13 +1671,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="54" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" customWidth="1"/>
+    <col min="7" max="7" width="20.1640625" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="10.83203125" customWidth="1"/>
+    <col min="10" max="10" width="14.33203125" customWidth="1"/>
+    <col min="11" max="11" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -1994,35 +2073,187 @@
         <v>55</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A50" s="2"/>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A53" s="2"/>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
         <v>60</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A60" s="37" t="s">
+        <v>221</v>
+      </c>
+      <c r="B60" s="37" t="s">
+        <v>213</v>
+      </c>
+      <c r="C60" s="37" t="s">
+        <v>214</v>
+      </c>
+      <c r="D60" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="E60" s="37" t="s">
+        <v>216</v>
+      </c>
+      <c r="F60" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="G60" s="37" t="s">
+        <v>217</v>
+      </c>
+      <c r="H60" s="37" t="s">
+        <v>163</v>
+      </c>
+      <c r="I60" s="37" t="s">
+        <v>218</v>
+      </c>
+      <c r="J60" s="37" t="s">
+        <v>219</v>
+      </c>
+      <c r="K60" s="37" t="s">
+        <v>220</v>
+      </c>
+      <c r="L60" s="37" t="s">
+        <v>222</v>
+      </c>
+      <c r="M60" s="37" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>66</v>
+      </c>
+      <c r="B61">
+        <f>BEDS_TOMATO</f>
+        <v>10</v>
+      </c>
+      <c r="C61">
+        <f>BEDS_CARROT+1</f>
+        <v>21</v>
+      </c>
+      <c r="D61">
+        <f>BEDS_MESCLUN</f>
+        <v>30</v>
+      </c>
+      <c r="E61" s="38">
+        <f>B61*HRS_PER_BED_WEEK_TOM*WEEKS*(1+DIM_PCT_TOM)^B61+C61*HRS_PER_BED_WEEK_CAR*WEEKS*(1+DIM_PCT_CAR)^C61+D61*HRS_PER_BED_WEEK_MES*WEEKS*(1+DIM_PCT_MES)^D61</f>
+        <v>5352.1828164171739</v>
+      </c>
+      <c r="F61" s="38">
+        <f>MIN(E61,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,E61-FARMER_FIELD_HRS)*TEMP_RATE</f>
+        <v>105419.84056279816</v>
+      </c>
+      <c r="G61" s="38">
+        <f>B61*PRICE_PER_BED_TOM+C61*PRICE_PER_BED_CAR+D61*PRICE_PER_BED_MES</f>
+        <v>212974</v>
+      </c>
+      <c r="H61" s="38">
+        <f>B61*FERTILIZER_PER_BED_TOM+C61*FERTILIZER_PER_BED_CAR+D61*FERTILIZER_PER_BED_MES</f>
+        <v>44440</v>
+      </c>
+      <c r="I61" s="38">
+        <f>G61-H61-F61-FIXED_COSTS</f>
+        <v>43114.159437201844</v>
+      </c>
+      <c r="J61" s="38">
+        <f>I61-SEASON_PROFIT</f>
+        <v>352.4947544568422</v>
+      </c>
+      <c r="K61">
+        <f>B61+C61+D61</f>
+        <v>61</v>
+      </c>
+      <c r="L61" s="38">
+        <f>MAX(0,E61-FARMER_FIELD_HRS)</f>
+        <v>4632.1828164171739</v>
+      </c>
+      <c r="M61" s="38" t="str">
+        <f>IF(AND(K61&lt;=TOTAL_BED_CAP,L61&lt;=MAX_TEMPS*TEMP_HRS_EACH),"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>67</v>
+      </c>
+      <c r="B62">
+        <f>BEDS_TOMATO</f>
+        <v>10</v>
+      </c>
+      <c r="C62">
+        <f>BEDS_CARROT</f>
+        <v>20</v>
+      </c>
+      <c r="D62">
+        <f>BEDS_MESCLUN+1</f>
+        <v>31</v>
+      </c>
+      <c r="E62" s="38">
+        <f>B62*HRS_PER_BED_WEEK_TOM*WEEKS*(1+DIM_PCT_TOM)^B62+C62*HRS_PER_BED_WEEK_CAR*WEEKS*(1+DIM_PCT_CAR)^C62+D62*HRS_PER_BED_WEEK_MES*WEEKS*(1+DIM_PCT_MES)^D62</f>
+        <v>5367.8512234393338</v>
+      </c>
+      <c r="F62" s="38">
+        <f>MIN(E62,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,E62-FARMER_FIELD_HRS)*TEMP_RATE</f>
+        <v>105691.86151804398</v>
+      </c>
+      <c r="G62" s="38">
+        <f>B62*PRICE_PER_BED_TOM+C62*PRICE_PER_BED_CAR+D62*PRICE_PER_BED_MES</f>
+        <v>213580</v>
+      </c>
+      <c r="H62" s="38">
+        <f>B62*FERTILIZER_PER_BED_TOM+C62*FERTILIZER_PER_BED_CAR+D62*FERTILIZER_PER_BED_MES</f>
+        <v>44880</v>
+      </c>
+      <c r="I62" s="38">
+        <f>G62-H62-F62-FIXED_COSTS</f>
+        <v>43008.138481956019</v>
+      </c>
+      <c r="J62" s="38">
+        <f>I62-SEASON_PROFIT</f>
+        <v>246.47379921101674</v>
+      </c>
+      <c r="K62">
+        <f>B62+C62+D62</f>
+        <v>61</v>
+      </c>
+      <c r="L62" s="38">
+        <f>MAX(0,E62-FARMER_FIELD_HRS)</f>
+        <v>4647.8512234393338</v>
+      </c>
+      <c r="M62" s="38" t="str">
+        <f>IF(AND(K62&lt;=TOTAL_BED_CAP,L62&lt;=MAX_TEMPS*TEMP_HRS_EACH),"PASS","FAIL")</f>
+        <v>PASS</v>
       </c>
     </row>
   </sheetData>
@@ -2480,7 +2711,7 @@
       </c>
       <c r="F7" s="20"/>
       <c r="G7" s="20">
-        <f t="shared" ref="G7:G27" si="4">PRICE_PER_BED_TOM</f>
+        <f t="shared" ref="G7:G28" si="4">PRICE_PER_BED_TOM</f>
         <v>8800</v>
       </c>
       <c r="H7" s="7"/>
@@ -2508,7 +2739,7 @@
       </c>
       <c r="P7" s="20"/>
       <c r="Q7" s="20">
-        <f t="shared" ref="Q7:Q27" si="9">PRICE_PER_BED_CAR</f>
+        <f t="shared" ref="Q7:Q28" si="9">PRICE_PER_BED_CAR</f>
         <v>2094</v>
       </c>
       <c r="R7" s="7"/>
@@ -2536,7 +2767,7 @@
       </c>
       <c r="Z7" s="20"/>
       <c r="AA7" s="20">
-        <f t="shared" ref="AA7:AA37" si="14">PRICE_PER_BED_MES</f>
+        <f t="shared" ref="AA7:AA38" si="14">PRICE_PER_BED_MES</f>
         <v>2700</v>
       </c>
       <c r="AB7" s="7"/>
@@ -4685,6 +4916,76 @@
       </c>
     </row>
     <row r="28" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A28" s="36">
+        <v>21</v>
+      </c>
+      <c r="B28" s="11">
+        <f t="shared" ref="B28" si="24">A28*HRS_PER_BED_WEEK_TOM*WEEKS*(1+DIM_PCT_TOM)^A28</f>
+        <v>13986.472394647943</v>
+      </c>
+      <c r="C28" s="20">
+        <f t="shared" ref="C28" si="25">MIN(B28,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,B28-FARMER_FIELD_HRS)*TEMP_RATE</f>
+        <v>255320.70129597123</v>
+      </c>
+      <c r="D28" s="20">
+        <f t="shared" ref="D28" si="26">A28*FERTILIZER_PER_BED_TOM</f>
+        <v>18480</v>
+      </c>
+      <c r="E28" s="20">
+        <f t="shared" ref="E28" si="27">C28+D28</f>
+        <v>273800.70129597123</v>
+      </c>
+      <c r="F28" s="20">
+        <f t="shared" ref="F28" si="28">E28-E27</f>
+        <v>33466.327879545948</v>
+      </c>
+      <c r="G28" s="20">
+        <f t="shared" si="4"/>
+        <v>8800</v>
+      </c>
+      <c r="H28" s="24">
+        <f t="shared" ref="H28" si="29">IF(F28&lt;=PRICE_PER_BED_TOM,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I28" s="24">
+        <f t="shared" ref="I28" si="30">I27*H28</f>
+        <v>0</v>
+      </c>
+      <c r="K28" s="36">
+        <v>21</v>
+      </c>
+      <c r="L28" s="11">
+        <f t="shared" ref="L28" si="31">K28*HRS_PER_BED_WEEK_CAR*WEEKS*(1+DIM_PCT_CAR)^K28</f>
+        <v>1058.1365663175229</v>
+      </c>
+      <c r="M28" s="20">
+        <f t="shared" ref="M28" si="32">MIN(L28,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,L28-FARMER_FIELD_HRS)*TEMP_RATE</f>
+        <v>30870.426498568107</v>
+      </c>
+      <c r="N28" s="20">
+        <f t="shared" ref="N28" si="33">K28*FERTILIZER_PER_BED_CAR</f>
+        <v>9240</v>
+      </c>
+      <c r="O28" s="20">
+        <f t="shared" ref="O28" si="34">M28+N28</f>
+        <v>40110.426498568107</v>
+      </c>
+      <c r="P28" s="20">
+        <f t="shared" ref="P28" si="35">O28-O27</f>
+        <v>1741.5052455431578</v>
+      </c>
+      <c r="Q28" s="20">
+        <f t="shared" si="9"/>
+        <v>2094</v>
+      </c>
+      <c r="R28" s="24">
+        <f t="shared" ref="R28" si="36">IF(P28&lt;=PRICE_PER_BED_CAR,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S28" s="24">
+        <f t="shared" ref="S28" si="37">S27*R28</f>
+        <v>0</v>
+      </c>
       <c r="U28" s="7">
         <v>21</v>
       </c>
@@ -5077,6 +5378,43 @@
       </c>
       <c r="AC37" s="24">
         <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="21:29" x14ac:dyDescent="0.2">
+      <c r="U38" s="36">
+        <v>31</v>
+      </c>
+      <c r="V38" s="11">
+        <f t="shared" ref="V38" si="38">U38*HRS_PER_BED_WEEK_MES*WEEKS*(1+DIM_PCT_MES)^U38</f>
+        <v>2050.3131451750946</v>
+      </c>
+      <c r="W38" s="20">
+        <f t="shared" ref="W38" si="39">MIN(V38,FARMER_FIELD_HRS)*FARMER_RATE+MAX(0,V38-FARMER_FIELD_HRS)*TEMP_RATE</f>
+        <v>48095.714325956505</v>
+      </c>
+      <c r="X38" s="20">
+        <f t="shared" ref="X38" si="40">U38*FERTILIZER_PER_BED_MES</f>
+        <v>27280</v>
+      </c>
+      <c r="Y38" s="20">
+        <f t="shared" ref="Y38" si="41">W38+X38</f>
+        <v>75375.714325956505</v>
+      </c>
+      <c r="Z38" s="20">
+        <f t="shared" ref="Z38" si="42">Y38-Y37</f>
+        <v>2453.5262007889978</v>
+      </c>
+      <c r="AA38" s="20">
+        <f t="shared" si="14"/>
+        <v>2700</v>
+      </c>
+      <c r="AB38" s="24">
+        <f t="shared" ref="AB38" si="43">IF(Z38&lt;=PRICE_PER_BED_MES,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AC38" s="24">
+        <f t="shared" ref="AC38" si="44">AC37*AB38</f>
         <v>0</v>
       </c>
     </row>
@@ -5106,7 +5444,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="52" customWidth="1"/>
@@ -5422,106 +5760,186 @@
         <v>199</v>
       </c>
     </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="30" t="s">
+        <v>225</v>
+      </c>
+      <c r="B19" s="34">
+        <f>352</f>
+        <v>352</v>
+      </c>
+      <c r="C19" s="35">
+        <f>SHADOW_CAR</f>
+        <v>352.4947544568422</v>
+      </c>
+      <c r="D19" s="33" t="str">
+        <f>IF(ABS(C19-B19)&lt;=5,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="E19" s="29" t="s">
+        <v>229</v>
+      </c>
+    </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="30" t="s">
+        <v>226</v>
+      </c>
+      <c r="B20" s="34">
+        <f>246</f>
+        <v>246</v>
+      </c>
+      <c r="C20" s="35">
+        <f>SHADOW_MES</f>
+        <v>246.47379921101674</v>
+      </c>
+      <c r="D20" s="33" t="str">
+        <f>IF(ABS(C20-B20)&lt;=5,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="E20" s="29" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="30" t="s">
+        <v>227</v>
+      </c>
+      <c r="B21" s="39">
+        <f>PRICE_PER_BED_CAR-MCSchedules!P28</f>
+        <v>352.49475445684226</v>
+      </c>
+      <c r="C21" s="35">
+        <f>SHADOW_CAR</f>
+        <v>352.4947544568422</v>
+      </c>
+      <c r="D21" s="33" t="str">
+        <f>IF(ABS(C21-B21)&lt;=1,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="E21" s="29" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" s="30" t="s">
+        <v>228</v>
+      </c>
+      <c r="B22" s="39">
+        <f>PRICE_PER_BED_MES-MCSchedules!Z38</f>
+        <v>246.47379921100023</v>
+      </c>
+      <c r="C22" s="35">
+        <f>SHADOW_MES</f>
+        <v>246.47379921101674</v>
+      </c>
+      <c r="D22" s="33" t="str">
+        <f>IF(ABS(C22-B22)&lt;=1,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="E22" s="29" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" s="3" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" s="2" t="s">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" s="2" t="s">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" s="2" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" s="2" t="s">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" s="2" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" s="2" t="s">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" s="2" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26" s="3" t="s">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" s="3" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27" s="4" t="s">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B31" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C31" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D31" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E31" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A28" s="7" t="s">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="B28" s="27">
+      <c r="B32" s="27">
         <v>10</v>
       </c>
-      <c r="C28" s="27">
+      <c r="C32" s="27">
         <v>20</v>
       </c>
-      <c r="D28" s="27">
+      <c r="D32" s="27">
         <v>30</v>
       </c>
-      <c r="E28" s="28">
+      <c r="E32" s="28">
         <f>SEASON_PROFIT</f>
         <v>42761.664682745002</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A29" s="7" t="s">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="B29" s="27">
+      <c r="B33" s="27">
         <v>10</v>
       </c>
-      <c r="C29" s="27">
+      <c r="C33" s="27">
         <v>20</v>
       </c>
-      <c r="D29" s="27">
+      <c r="D33" s="27">
         <v>30</v>
       </c>
-      <c r="E29" s="28">
+      <c r="E33" s="28">
         <f>SEASON_PROFIT</f>
         <v>42761.664682745002</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A31" s="29" t="s">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35" s="29" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A32" s="29" t="s">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" s="29" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A33" s="29" t="s">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" s="29" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A34" s="29" t="s">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" s="29" t="s">
         <v>212</v>
       </c>
     </row>

--- a/capabilities/marginal-analysis/model.xlsx
+++ b/capabilities/marginal-analysis/model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/seanbarnes/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61709E9A-6F66-674D-A0B4-90B1D7E7D945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06224F4A-7239-614A-AD04-8904C5B5AF89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6660" yWindow="680" windowWidth="25800" windowHeight="19580" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7940" yWindow="1260" windowWidth="25800" windowHeight="19580" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,12 @@
     <sheet name="Checks" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">MCSchedules!$AA$7:$AA$38</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">MCSchedules!$U$7:$U$38</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">MCSchedules!$Z$7:$Z$38</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">MCSchedules!$AA$7:$AA$38</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">MCSchedules!$U$7:$U$38</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">MCSchedules!$Z$7:$Z$38</definedName>
     <definedName name="BEDS_CARROT">Optimization!$B$6</definedName>
     <definedName name="BEDS_MESCLUN">Optimization!$B$7</definedName>
     <definedName name="BEDS_TOMATO">Optimization!$B$5</definedName>
@@ -1018,7 +1024,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyFont="1" numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1035,6 +1041,3569 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>tomato-mc-vs-pricing</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>MCSchedules!$A$7:$A$28</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>21</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1469-A64F-B975-C750F934FDE6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>MCSchedules!$F$7:$F$28</c:f>
+              <c:numCache>
+                <c:formatCode>\$#,##0;\(\$#,##0\);\-</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="1">
+                  <c:v>4317.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5005</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5795.6250000000036</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6703.125</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7660.859375</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4906.2750000000051</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5585.7089062500017</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6360.7668437500033</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7243.7792796875074</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8248.586534375012</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9390.7174472031256</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>10687.588677253138</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>12158.726978841107</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>13826.017053974152</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15713.977874345364</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17850.070688251115</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>20265.042286194512</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>22993.307496844121</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>26073.375326761772</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>29548.323647694342</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>33466.327879545948</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-1469-A64F-B975-C750F934FDE6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>MCSchedules!$G$7:$G$28</c:f>
+              <c:numCache>
+                <c:formatCode>\$#,##0;\(\$#,##0\);\-</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>8800</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-1469-A64F-B975-C750F934FDE6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="2001214463"/>
+        <c:axId val="2001214911"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="2001214463"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2001214911"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2001214911"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2001214463"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>carrots-mc-vs-price</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>MCSchedules!$K$7:$K$28</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>21</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2D13-AC49-A41C-80AAC7862CDF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>MCSchedules!$P$7:$P$28</c:f>
+              <c:numCache>
+                <c:formatCode>\$#,##0;\(\$#,##0\);\-</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="1">
+                  <c:v>1507.7083333333333</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1561.0937499999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1616.481119791667</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1673.9371744791652</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1733.530731201171</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1795.332755025227</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1859.4164233334868</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1925.8571920852646</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1994.7328640100477</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2066.1236587860258</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2140.1122852607878</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2216.7840157725441</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2296.2267626316061</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2378.5311568237667</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2463.7906289988823</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2552.1014928097429</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1670.9013431626554</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1589.1387909931072</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1638.1753169880685</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1688.9454575384007</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1741.5052455431578</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-2D13-AC49-A41C-80AAC7862CDF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>MCSchedules!$Q$7:$Q$28</c:f>
+              <c:numCache>
+                <c:formatCode>\$#,##0;\(\$#,##0\);\-</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2094</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-2D13-AC49-A41C-80AAC7862CDF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="2001121535"/>
+        <c:axId val="1985381695"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="2001121535"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1985381695"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1985381695"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2001121535"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>mesclun-mc-vs-price</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>MCSchedules!$U$7:$U$38</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>31</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6A8E-E546-9D69-B8CEA0EBE2EB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>MCSchedules!$Z$7:$Z$38</c:f>
+              <c:numCache>
+                <c:formatCode>\$#,##0;\(\$#,##0\);\-</c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="1">
+                  <c:v>2462.03125</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2501.58203125</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2541.8743896484366</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2582.920684814454</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2624.7334694862348</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2667.3254924178127</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2710.7097013180683</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2754.8992458326466</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2799.9074805692508</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2845.7479681671139</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2892.4344824110776</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2939.9810113911262</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2988.4017607077876</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2522.5810943551696</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1983.9619249331008</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2009.5273589841818</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2035.5594348357699</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2062.0658239338081</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2089.0543165975978</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2116.532823793008</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2144.5093789313105</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2172.9921396943828</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2201.9893898860464</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2231.5095413106901</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2261.5611356787776</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2292.1528465402444</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2323.2934812457679</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2354.9919829366991</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2387.2574325634341</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2420.0990509335097</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2453.5262007889978</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-6A8E-E546-9D69-B8CEA0EBE2EB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>MCSchedules!$AA$7:$AA$38</c:f>
+              <c:numCache>
+                <c:formatCode>\$#,##0;\(\$#,##0\);\-</c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>2700</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2700</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2700</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2700</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2700</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2700</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2700</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2700</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2700</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2700</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2700</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2700</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2700</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2700</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2700</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2700</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2700</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2700</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2700</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2700</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2700</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2700</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2700</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2700</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2700</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2700</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2700</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2700</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2700</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2700</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2700</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2700</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-6A8E-E546-9D69-B8CEA0EBE2EB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="2001925247"/>
+        <c:axId val="2001924351"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="2001925247"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2001924351"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2001924351"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2001925247"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>317500</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>622300</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1EEDF97E-CB0F-599D-B8EA-4627725171F8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>412750</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>565150</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F820DDC0-6B04-BD12-D6A0-4690F32D5083}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>222250</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>374650</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F30F6162-8976-118B-DCB0-D91F245AB2F5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5439,6 +9008,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/capabilities/marginal-analysis/model.xlsx
+++ b/capabilities/marginal-analysis/model.xlsx
@@ -1078,7 +1078,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>tomato-mc-vs-pricing</a:t>
+              <a:t>Tomato marginal cost against price</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1121,103 +1121,17 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:val>
-            <c:numRef>
-              <c:f>MCSchedules!$A$7:$A$28</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>MCSchedules!$F$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>21</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-1469-A64F-B975-C750F934FDE6}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
+                  <c:v>Marginal cost</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
@@ -1230,6 +1144,81 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>MCSchedules!$A$7:$A$28</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>21</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
           <c:val>
             <c:numRef>
               <c:f>MCSchedules!$F$7:$F$28</c:f>
@@ -1310,8 +1299,19 @@
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>MCSchedules!$G$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Price per bed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
@@ -1324,6 +1324,81 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>MCSchedules!$A$7:$A$28</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>21</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
           <c:val>
             <c:numRef>
               <c:f>MCSchedules!$G$7:$G$28</c:f>
@@ -1425,6 +1500,32 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Tomato beds planted</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1475,6 +1576,32 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Dollars per bed</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
         <c:majorGridlines>
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -1642,7 +1769,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>carrots-mc-vs-price</a:t>
+              <a:t>Carrot marginal cost against price</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1685,103 +1812,17 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:val>
-            <c:numRef>
-              <c:f>MCSchedules!$K$7:$K$28</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>MCSchedules!$P$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>21</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-2D13-AC49-A41C-80AAC7862CDF}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
+                  <c:v>Marginal cost</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
@@ -1794,6 +1835,81 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>MCSchedules!$K$7:$K$28</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>21</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
           <c:val>
             <c:numRef>
               <c:f>MCSchedules!$P$7:$P$28</c:f>
@@ -1874,8 +1990,19 @@
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>MCSchedules!$Q$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Price per bed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
@@ -1888,6 +2015,81 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>MCSchedules!$K$7:$K$28</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>21</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
           <c:val>
             <c:numRef>
               <c:f>MCSchedules!$Q$7:$Q$28</c:f>
@@ -1989,6 +2191,32 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Carrot beds planted</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2039,6 +2267,32 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Dollars per bed</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
         <c:majorGridlines>
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -2206,7 +2460,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>mesclun-mc-vs-price</a:t>
+              <a:t>Mesclun marginal cost against price</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -2249,133 +2503,17 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:val>
-            <c:numRef>
-              <c:f>MCSchedules!$U$7:$U$38</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="32"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>MCSchedules!$Z$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>24</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>26</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>27</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>28</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>29</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>31</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-6A8E-E546-9D69-B8CEA0EBE2EB}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
+                  <c:v>Marginal cost</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
@@ -2388,6 +2526,111 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>MCSchedules!$U$7:$U$38</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>31</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
           <c:val>
             <c:numRef>
               <c:f>MCSchedules!$Z$7:$Z$38</c:f>
@@ -2498,8 +2741,19 @@
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>MCSchedules!$AA$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Price per bed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
@@ -2512,6 +2766,111 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>MCSchedules!$U$7:$U$38</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>31</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
           <c:val>
             <c:numRef>
               <c:f>MCSchedules!$AA$7:$AA$38</c:f>
@@ -2643,6 +3002,32 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Mesclun beds planted</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2693,6 +3078,32 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Dollars per bed</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
         <c:majorGridlines>
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">

--- a/capabilities/marginal-analysis/model.xlsx
+++ b/capabilities/marginal-analysis/model.xlsx
@@ -18,6 +18,7 @@
     <sheet name="CostStructure" sheetId="3" r:id="rId3"/>
     <sheet name="MCSchedules" sheetId="4" r:id="rId4"/>
     <sheet name="Checks" sheetId="5" r:id="rId5"/>
+    <sheet name="AVC" sheetId="6" r:id="rId100"/>
   </sheets>
   <definedNames>
     <definedName name="_xlchart.v1.0" hidden="1">MCSchedules!$AA$7:$AA$38</definedName>
@@ -131,7 +132,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="249">
   <si>
     <t>Optimization</t>
   </si>
@@ -824,6 +825,60 @@
   </si>
   <si>
     <t>Two routes through the model, no shared formula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average variable cost and standalone profit — Section 4 of the analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variable cost is the standalone total cost from MC schedules, which excludes fixed costs per 3.10.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Left half: does each bed clear its own variable cost? Right half: does the crop cover all $20,000 alone?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price per bed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variable cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price - AVC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standalone profit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tomatoes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carrots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mesclun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every crop's AVC is below its price, so every bed contributes toward fixed costs the farm owes anyway.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carrots and mesclun lose money standalone only because each is asked to carry the whole $20,000 alone.</t>
   </si>
 </sst>
 </file>
@@ -9927,4 +9982,197 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="10" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="s">
+        <v>234</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>235</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>236</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>238</v>
+      </c>
+      <c r="F5" s="0" t="s">
+        <v>239</v>
+      </c>
+      <c r="G5" s="0" t="s">
+        <v>240</v>
+      </c>
+      <c r="H5" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="I5" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="J5" s="0" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="B6" s="0">
+        <f>BEDS_TOMATO</f>
+        <v>10</v>
+      </c>
+      <c r="C6" s="0">
+        <f>PRICE_PER_BED_TOM</f>
+        <v>8800</v>
+      </c>
+      <c r="D6" s="0">
+        <f>MCSchedules!E17</f>
+        <v>61827.225911458326</v>
+      </c>
+      <c r="E6" s="0">
+        <f>D6/B6</f>
+        <v>6182.7225911458326</v>
+      </c>
+      <c r="F6" s="0">
+        <f>C6-E6</f>
+        <v>2617.2774088541674</v>
+      </c>
+      <c r="G6" s="0">
+        <f>B6*C6</f>
+        <v>88000</v>
+      </c>
+      <c r="H6" s="0">
+        <f>FIXED_COSTS</f>
+        <v>20000</v>
+      </c>
+      <c r="I6" s="0">
+        <f>D6+H6</f>
+        <v>81827.225911458326</v>
+      </c>
+      <c r="J6" s="0">
+        <f>G6-I6</f>
+        <v>6172.7740885416744</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="B7" s="0">
+        <f>BEDS_CARROT</f>
+        <v>20</v>
+      </c>
+      <c r="C7" s="0">
+        <f>PRICE_PER_BED_CAR</f>
+        <v>2094</v>
+      </c>
+      <c r="D7" s="0">
+        <f>MCSchedules!O27</f>
+        <v>38368.921339068096</v>
+      </c>
+      <c r="E7" s="0">
+        <f>D7/B7</f>
+        <v>1918.4460669534048</v>
+      </c>
+      <c r="F7" s="0">
+        <f>C7-E7</f>
+        <v>175.55393304659518</v>
+      </c>
+      <c r="G7" s="0">
+        <f>B7*C7</f>
+        <v>41880</v>
+      </c>
+      <c r="H7" s="0">
+        <f>FIXED_COSTS</f>
+        <v>20000</v>
+      </c>
+      <c r="I7" s="0">
+        <f>D7+H7</f>
+        <v>58368.921339068096</v>
+      </c>
+      <c r="J7" s="0">
+        <f>G7-I7</f>
+        <v>-16488.921339068096</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="s">
+        <v>246</v>
+      </c>
+      <c r="B8" s="0">
+        <f>BEDS_MESCLUN</f>
+        <v>30</v>
+      </c>
+      <c r="C8" s="0">
+        <f>PRICE_PER_BED_MES</f>
+        <v>2700</v>
+      </c>
+      <c r="D8" s="0">
+        <f>MCSchedules!Y37</f>
+        <v>72922.188096525</v>
+      </c>
+      <c r="E8" s="0">
+        <f>D8/B8</f>
+        <v>2430.7396032175</v>
+      </c>
+      <c r="F8" s="0">
+        <f>C8-E8</f>
+        <v>269.2603967825</v>
+      </c>
+      <c r="G8" s="0">
+        <f>B8*C8</f>
+        <v>81000</v>
+      </c>
+      <c r="H8" s="0">
+        <f>FIXED_COSTS</f>
+        <v>20000</v>
+      </c>
+      <c r="I8" s="0">
+        <f>D8+H8</f>
+        <v>92922.188096525</v>
+      </c>
+      <c r="J8" s="0">
+        <f>G8-I8</f>
+        <v>-11922.188096525</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="s">
+        <v>248</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/capabilities/marginal-analysis/model.xlsx
+++ b/capabilities/marginal-analysis/model.xlsx
@@ -875,7 +875,7 @@
     <t xml:space="preserve">Mesclun</t>
   </si>
   <si>
-    <t xml:space="preserve">Every crop's AVC is below its price, so every bed contributes toward fixed costs the farm owes anyway.</t>
+    <t xml:space="preserve">At the planted bed counts every crop's AVC is below its price, so each crop covers its variable cost and contributes the difference toward fixed costs the farm owes anyway. Not true at every quantity: mesclun AVC exceeds price at beds 13-14 and tomato AVC from bed 16 up.</t>
   </si>
   <si>
     <t xml:space="preserve">Carrots and mesclun lose money standalone only because each is asked to carry the whole $20,000 alone.</t>
